--- a/listes/Medicaments_Onco360.xlsx
+++ b/listes/Medicaments_Onco360.xlsx
@@ -5,7 +5,7 @@
     <sheet name="Médicaments" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Médicaments!$A$1:$D$148</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Médicaments!$A$1:$C$163</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -38,7 +38,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2B3"/>
+        <fgColor rgb="FFDFF3E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -80,10 +80,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="46" customWidth="1"/>
-    <col min="2" max="2" width="72" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="58" customWidth="1"/>
+    <col min="1" max="1" width="48" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -102,11 +101,6 @@
           <t xml:space="preserve">Classe thérapeutique</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Remarque (ce qui a changé / à vérifier)</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr" s="2">
@@ -124,31 +118,21 @@
           <t xml:space="preserve">Hormonothérapie anticancéreuse (inhibiteur de la synthèse des androgènes)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr" s="3">
+      <c r="A3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ALER-Z (cétirizine) 10 mg</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">1 comprimé le soir pendant … (durée à compléter)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr" s="3">
+      <c r="B3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 comprimé le soir pendant …</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Antihistaminique H1 (antiallergique)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Votre texte s'arrêtait à « pendant » : durée à compléter. Nom commercial au Maroc : ALER-Z (vous aviez écrit ALLER-Z).</t>
         </is>
       </c>
     </row>
@@ -160,17 +144,12 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé le soir, la veille du traitement</t>
+          <t xml:space="preserve">1 comprimé le soir</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Anxiolytique (benzodiazépine)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -182,39 +161,29 @@
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Au début : 25 à 75 mg le soir, puis augmenter progressivement jusqu'à 75 mg matin et soir (soit 150 mg par jour), pendant 1 mois</t>
+          <t xml:space="preserve">Au début : 75 mg le soir, puis augmenter progressivement après 3 jours si bonne tolérance à 75 mg matin et soir (soit 150 mg par jour), pendant 1 mois</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Antiépileptique (douleurs neuropathiques)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">APAZIDE</t>
+          <t xml:space="preserve">ANDROCUR (cyprotérone) 50 mg</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">1 gélule matin et soir (soit 2 gélules par jour) pendant 7 jours</t>
+          <t xml:space="preserve">2 comprimés matin et soir (soit 4 comprimés = 200 mg par jour), à commencer 1 semaine avant la 1re injection d'agoniste de la LH-RH, pendant 3 semaines au total</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Médicament introuvable sur les sites marocains : nom et classe à vérifier.</t>
+          <t xml:space="preserve">Hormonothérapie anticancéreuse (anti-androgène)</t>
         </is>
       </c>
     </row>
@@ -234,11 +203,6 @@
           <t xml:space="preserve">Antianémique (stimulant de l'érythropoïèse)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr" s="2">
@@ -256,2075 +220,1600 @@
           <t xml:space="preserve">Anti-inflammatoire non stéroïdien (coxib)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AUGMENTIN (amoxicilline + acide clavulanique) 1 g</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1 comprimé (1 g) matin, midi et soir (soit 3 comprimés par jour) pendant 5 jours</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Antibiotique (pénicilline + inhibiteur de bêta-lactamase)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="A9" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ARIMIDEX (anastrozole) 1 mg</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">1 comprimé par jour, à heure fixe, pendant 3 mois</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Hormonothérapie anticancéreuse (anti-aromatase)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">BACTRIM FORTE (sulfaméthoxazole + triméthoprime)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1 comprimé le lundi, le mercredi et le vendredi, pendant 3 mois</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Antibiotique (sulfamide), prévention de la pneumocystose</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="A10" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">AROMASINE (exémestane) 25 mg</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">1 comprimé par jour, après un repas, à heure fixe, pendant 3 mois</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Hormonothérapie anticancéreuse (anti-aromatase)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BANDE VELPEAU 15 x 10 cm</t>
+          <t xml:space="preserve">AUGMENTIN (amoxicilline + acide clavulanique) 1 g</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">À appliquer sur les compresses pour maintenir les pansements en place</t>
+          <t xml:space="preserve">1 comprimé (1 g) matin, midi et soir (soit 3 comprimés par jour) pendant 5 jours</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Dispositif médical (pansement)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">2 lignes fusionnées.</t>
+          <t xml:space="preserve">Antibiotique (pénicilline + inhibiteur de bêta-lactamase)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BETADINE 10 % gynécologique (povidone iodée)</t>
+          <t xml:space="preserve">BACTRIM FORTE (sulfaméthoxazole + triméthoprime)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 à 2 bouchons dilués dans 1 litre d'eau tiède (une bassine), en bain de siège ou en irrigation de 5 à 10 minutes, pendant 3 mois</t>
+          <t xml:space="preserve">1 comprimé le lundi, le mercredi et le vendredi, pendant 3 mois</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antiseptique (povidone iodée)</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">2 lignes fusionnées (l'une précisait 1 litre et l'irrigation, l'autre la durée de 3 mois).</t>
+          <t xml:space="preserve">Antibiotique (sulfamide), prévention de la pneumocystose</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BICARBONATE DE SODIUM 14 ‰ + XYLOCAÏNE 2 % (± FUNGIZONE)</t>
+          <t xml:space="preserve">BANDE VELPEAU 15 x 10 cm</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Bains de bouche après les repas, ou au moins 1 heure avant les repas</t>
+          <t xml:space="preserve">À appliquer sur les compresses pour maintenir les pansements en place</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Bain de bouche (alcalin + anesthésique local ± antifongique)</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">2 lignes identiques fusionnées.</t>
+          <t xml:space="preserve">Dispositif médical (pansement)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BICARBONATE DE SODIUM 14 ‰, 500 ml</t>
+          <t xml:space="preserve">BETADINE 10 % gynécologique (povidone iodée)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Bains de bouche au moins 6 fois par jour, pendant toute la radiothérapie et jusqu'à 3 mois après (seul ou associé)</t>
+          <t xml:space="preserve">1 à 2 bouchons dilués dans 1 litre d'eau tiède (une bassine), en bain de siège ou en irrigation de 5 à 10 minutes, pendant 1 mois</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Bain de bouche alcalin (prévention de la mucite)</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Antiseptique (povidone iodée)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">BUFREN (ibuprofène) 400 mg</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1 comprimé matin et soir (soit 2 comprimés par jour) pendant 1 semaine</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Anti-inflammatoire non stéroïdien</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">4 lignes : 2 posologies différentes gardées (celle-ci, et « en cas de douleur » ci-dessous).</t>
+      <c r="A15" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">BIAFINE émulsion (trolamine)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">2 à 3 applications par jour en couche épaisse sur la zone irradiée, à faire pénétrer par un léger massage ; pas d'application dans les 2 heures qui précèdent la séance</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Soin de la radiodermite</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BUFREN (ibuprofène) 400 mg</t>
+          <t xml:space="preserve">BICARBONATE DE SODIUM 14 ‰ + XYLOCAÏNE 2 %</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé matin et soir en cas de douleur (maximum 2 comprimés par jour)</t>
+          <t xml:space="preserve">Bains de bouche après les repas, ou au moins 1 heure avant les repas</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Anti-inflammatoire non stéroïdien</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Variante « à la demande ».</t>
+          <t xml:space="preserve">Bain de bouche (alcalin + anesthésique local)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CACIT VITAMINE D3 1000 mg / 880 UI</t>
+          <t xml:space="preserve">BICARBONATE DE SODIUM 14 ‰, 500 ml</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé par jour, le matin, pendant 3 mois</t>
+          <t xml:space="preserve">Bains de bouche au moins 6 fois par jour, pendant toute la radiothérapie et jusqu'à 3 mois après (seul ou associé)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Calcium + vitamine D</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">2 lignes fusionnées (l'une sans durée).</t>
+          <t xml:space="preserve">Bain de bouche alcalin (prévention de la mucite)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CASODEX (bicalutamide) 50 mg</t>
+          <t xml:space="preserve">BUFREN (ibuprofène) 400 mg</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé par jour, le matin, pendant 1 mois, puis arrêt</t>
+          <t xml:space="preserve">1 comprimé matin et soir en cas de douleur (maximum 2 comprimés par jour)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Hormonothérapie anticancéreuse (anti-androgène)</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Anti-inflammatoire non stéroïdien</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">CEDOL (paracétamol 400 mg + codéine 20 mg)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">1 comprimé en cas de douleur, maximum 4 comprimés par jour, pendant 3 mois</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Antalgique de palier 2 (paracétamol + codéine)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Vos lignes « CEDOL 400 mg » et « CEDOL 20 mg » sont le même médicament (400 mg de paracétamol + 20 mg de codéine) : 2 posologies gardées.</t>
+      <c r="A19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CACIT VITAMINE D3 1000 mg / 880 UI</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 comprimé par jour, le matin, pendant 3 mois</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Calcium + vitamine D</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">CEDOL (paracétamol 400 mg + codéine 20 mg)</t>
+          <t xml:space="preserve">CAPÉCITABINE (XELODA) 500 mg / 150 mg</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2 comprimés en cas de douleur, 3 fois par jour (soit 2 comprimés toutes les 8 heures, maximum 6 comprimés par jour)</t>
+          <t xml:space="preserve">… comprimés de 500 mg et … comprimés de 150 mg le matin et le soir (… mg/m² 2 fois par jour), dans les 30 minutes qui suivent le repas, de J1 à J14, puis 7 jours d'arrêt (reprise à J22)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">Antalgique de palier 2 (paracétamol + codéine)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Variante (ancienne ligne « CEDOL 20 mg »).</t>
+          <t xml:space="preserve">Chimiothérapie orale (fluoropyrimidine)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">CETRA (tramadol 37,5 mg + paracétamol 325 mg)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1 comprimé en cas de pic de douleur, maximum 4 comprimés par jour</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Antalgique de palier 2 (tramadol + paracétamol)</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">4 lignes fusionnées (CETRA 37,5 mg et CETRA 325 mg sont le même comprimé).</t>
+      <c r="A21" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">CAPÉCITABINE (XELODA) 500 mg / 150 mg, avec la radiothérapie</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">… comprimés de 500 mg et … comprimés de 150 mg le matin et le soir (825 mg/m² 2 fois par jour), dans les 30 minutes qui suivent le repas, chaque jour de radiothérapie</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Chimiothérapie orale (fluoropyrimidine)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHEMOSET (ondansétron) 8 mg</t>
+          <t xml:space="preserve">CASODEX (bicalutamide) 50 mg</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé matin et soir (soit 2 comprimés par jour) à J1, J2 et J3 après la chimiothérapie (pendant 3 jours)</t>
+          <t xml:space="preserve">1 comprimé par jour, le matin, pendant 1 mois, puis arrêt</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antiémétique (sétron, anti-5HT3)</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Hormonothérapie anticancéreuse (anti-androgène)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CLOPRAME (métoclopramide) 10 mg</t>
+          <t xml:space="preserve">CEDOL (paracétamol 400 mg + codéine 20 mg)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé en cas de nausées, maximum 3 comprimés par jour (espacés d'au moins 3 heures)</t>
+          <t xml:space="preserve">1 comprimé en cas de douleur, maximum 4 comprimés par jour, pendant 3 mois</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antiémétique (antidopaminergique)</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Antalgique de palier 2 (paracétamol + codéine)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COMPRESSES NON TISSÉES 10 x 10 cm</t>
+          <t xml:space="preserve">CETRA (tramadol 37,5 mg + paracétamol 325 mg)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">À appliquer après nettoyage soigneux et séchage de la plaie ; à changer tous les jours</t>
+          <t xml:space="preserve">1 comprimé en cas de pic de douleur, maximum 4 comprimés par jour</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Dispositif médical (pansement)</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">2 lignes fusionnées.</t>
+          <t xml:space="preserve">Antalgique de palier 2 (tramadol + paracétamol)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">COTIPRED (prednisolone) 20 mg</t>
+          <t xml:space="preserve">CHEMOSET (ondansétron) 8 mg</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé le matin</t>
+          <t xml:space="preserve">1 comprimé matin et soir (soit 2 comprimés par jour) à J1, J2 et J3 après la chimiothérapie (pendant 3 jours)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Corticoïde</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">3 lignes : 2 posologies différentes gardées.</t>
+          <t xml:space="preserve">Antiémétique (sétron, anti-5HT3)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">COTIPRED (prednisolone) 20 mg</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">3 comprimés le matin (soit 60 mg par jour) pendant … (durée à compléter)</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Corticoïde</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Votre texte s'arrêtait à « pendant » : durée à compléter. Vous aviez écrit « à jeun » : le corticoïde se prend d'habitude au petit-déjeuner, à vérifier.</t>
+      <c r="A26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CLOPRAME (métoclopramide) 10 mg</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 comprimé en cas de nausées, maximum 3 comprimés par jour (espacés d'au moins 3 heures)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Antiémétique (antidopaminergique)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">COTIPRED (prednisolone) 60 mg</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">1 comprimé le matin pendant 5 jours</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Corticoïde</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Dosage de 60 mg à vérifier (COTIPRED existe surtout en 5 et 20 mg).</t>
+      <c r="A27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">COMPRESSES NON TISSÉES 10 x 10 cm</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">À appliquer après nettoyage soigneux et séchage de la plaie ; à changer tous les jours</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Dispositif médical (pansement)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">D-CURE FORTE 100 000 UI, solution buvable</t>
+          <t xml:space="preserve">COTIPRED (prednisolone) 20 mg</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 ampoule par mois, à boire sur un sucre</t>
+          <t xml:space="preserve">3 comprimés le matin (soit 60 mg par jour) pendant …</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Vitamine D</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Corticoïde</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">D-CURE FORTE 25 000 UI, solution buvable</t>
+          <t xml:space="preserve">D-CURE FORTE 100 000 UI, solution buvable</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2 ampoules par semaine, à boire sur un sucre, pendant 3 mois</t>
+          <t xml:space="preserve">1 ampoule par mois, à boire sur un sucre</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Vitamine D</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">D3NORM 200</t>
+          <t xml:space="preserve">D-CURE FORTE 25 000 UI, solution buvable</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 gouttes par jour pendant 3 mois</t>
+          <t xml:space="preserve">2 ampoules par semaine, à boire sur un sucre, pendant 3 mois</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Vitamine D</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAROLUTAMIDE (NUBEQA) 300 mg</t>
+          <t xml:space="preserve">D3NORM 200</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2 comprimés le matin et 2 comprimés le soir (soit 4 comprimés = 1 200 mg par jour)</t>
+          <t xml:space="preserve">10 gouttes par jour pendant 3 mois</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Hormonothérapie anticancéreuse (anti-androgène)</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Vitamine D</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">DAROLUTAMIDE (NUBEQA) 300 mg</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">2 comprimés le matin et 2 comprimés le soir (soit 4 comprimés = 1 200 mg par jour)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Hormonothérapie anticancéreuse (anti-androgène)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DAYLONG écran total</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr" s="2">
+      <c r="B33" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1 application le matin, avant de sortir</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr" s="2">
+      <c r="C33" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Protection solaire</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr" s="3">
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">DECAPEPTYL LP (triptoréline) 11,25 mg</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr" s="3">
+      <c r="B34" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1 injection tous les 3 mois</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr" s="3">
+      <c r="C34" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Hormonothérapie anticancéreuse (agoniste de la LH-RH)</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Vous aviez écrit « SC » : DECAPEPTYL LP s'injecte en intramusculaire. Voie retirée du texte, à vérifier.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr" s="3">
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">DECAPEPTYL LP (triptoréline) 22,5 mg</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr" s="3">
+      <c r="B35" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1 injection tous les 6 mois</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr" s="3">
+      <c r="C35" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Hormonothérapie anticancéreuse (agoniste de la LH-RH)</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Même remarque : voie intramusculaire, à vérifier.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr" s="3">
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">DECAPEPTYL LP (triptoréline) 3 mg</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">1 injection intramusculaire tous les 28 jours</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Hormonothérapie anticancéreuse (agoniste de la LH-RH)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">DEXAMÉTHASONE 4 mg, comprimé</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">2 comprimés le matin (soit 8 mg) à J2 et J3 après la chimiothérapie</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Corticoïde (antiémétique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">DEXAMÉTHASONE 4 mg, comprimé (œdème cérébral)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">… comprimés le matin (… mg par jour), puis diminution progressive selon l'évolution</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Corticoïde</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">DEXERYL</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr" s="3">
+      <c r="B39" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1 application matin et soir (soit 2 applications par jour)</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr" s="3">
+      <c r="C39" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Émollient (peau sèche)</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Votre texte disait « 1 application par jour, le matin et soir » : corrigé en 2 par jour, à vérifier.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">DICYNONE (étamsylate) 500 mg</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1 comprimé matin, midi et soir (soit 3 comprimés par jour) pendant 8 jours</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Hémostatique</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Répartition matin / midi / soir ajoutée (votre texte : 3 comprimés par jour).</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">DIFFERINE (adapalène) crème</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1 application le soir, un jour sur deux, sur les boutons</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Antiacnéique (rétinoïde local)</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">DOXYMYCINE (doxycycline) 100 mg</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1 comprimé par jour pendant 1 mois</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Antibiotique (cycline)</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">DUOXOL 500 mg / 2 mg</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Selon prescription médicale (à préciser)</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Médicament introuvable sur les sites marocains, sans posologie : à compléter ou à retirer.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DUPHALAC (lactulose), sachet</t>
+          <t xml:space="preserve">DICYNONE (étamsylate) 500 mg</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 à 3 sachets par jour (matin, midi et soir) en cas de constipation importante</t>
+          <t xml:space="preserve">1 comprimé matin, midi et soir (soit 3 comprimés par jour) pendant 8 jours</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Laxatif osmotique</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">3 lignes identiques fusionnées.</t>
+          <t xml:space="preserve">Hémostatique</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EDEX (alprostadil) 10 µg</t>
+          <t xml:space="preserve">DIFFERINE (adapalène) crème</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 injection intracaverneuse 5 à 10 minutes avant le rapport, maximum 1 injection par jour</t>
+          <t xml:space="preserve">1 application le soir, un jour sur deux, sur les boutons</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Traitement de la dysfonction érectile</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Antiacnéique (rétinoïde local)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EFFIPRED (prednisolone) 5 mg</t>
+          <t xml:space="preserve">DOXYMYCINE (doxycycline) 100 mg</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé par jour, le matin, en même temps que l'abiratérone</t>
+          <t xml:space="preserve">1 comprimé par jour pendant 1 mois</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Corticoïde</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Antibiotique (cycline)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EMEND (aprépitant) 125 mg / 80 mg</t>
+          <t xml:space="preserve">DUPHALAC (lactulose) sirop</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 gélule de 125 mg à J1 de la chimiothérapie, puis 1 gélule de 80 mg à J2 et à J3</t>
+          <t xml:space="preserve">1 à 3 cuillères par jour (matin, midi et soir) en cas de constipation importante</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antiémétique (anti-NK1)</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">EMEND se présente en gélules (« comprimé » corrigé).</t>
+          <t xml:space="preserve">Laxatif osmotique</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EOSINE aqueuse 2 %, unidose 2 ml</t>
+          <t xml:space="preserve">DUPHALAC (lactulose), sachet</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 à 2 applications par jour sur les lésions suintantes, à l'aide d'une compresse stérile</t>
+          <t xml:space="preserve">1 à 3 sachets par jour (matin, midi et soir) en cas de constipation importante</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antiseptique asséchant</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">4 lignes identiques fusionnées.</t>
+          <t xml:space="preserve">Laxatif osmotique</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">EPYCA (prégabaline) 75 mg</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Au début : 25 à 75 mg le soir, puis augmenter progressivement jusqu'à 75 mg matin et soir (soit 150 mg par jour), pendant 1 mois</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Antiépileptique (douleurs neuropathiques)</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="A45" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">DUROGESIC (fentanyl) 12 / 25 / 50 µg/h, patch</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">1 patch à changer toutes les 72 heures (3 jours)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Antalgique de palier 3 (opioïde transdermique)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ERLEADA (apalutamide) 60 mg</t>
+          <t xml:space="preserve">EDEX (alprostadil) 10 µg</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4 comprimés par jour en une seule prise (soit 240 mg par jour)</t>
+          <t xml:space="preserve">1 injection intracaverneuse 5 à 10 minutes avant le rapport, maximum 1 injection par jour</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Hormonothérapie anticancéreuse (anti-androgène)</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Traitement de la dysfonction érectile</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EUCARBON, comprimé</t>
+          <t xml:space="preserve">EFFIPRED (prednisolone) 5 mg</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé matin, midi et soir (soit 3 comprimés par jour), les 2 jours précédant le traitement</t>
+          <t xml:space="preserve">1 comprimé par jour, le matin, en même temps que l'abiratérone</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Laxatif / adsorbant intestinal (charbon végétal, séné)</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Nom « EUCARBON 30 CPS » simplifié (30 = nombre de comprimés de la boîte).</t>
+          <t xml:space="preserve">Corticoïde</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">FAZOL (isoconazole) 2 % crème, 30 g</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Appliquer entre les orteils … fois par jour pendant 10 jours, puis réévaluer</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Antifongique local</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Nombre d'applications par jour à préciser.</t>
+      <c r="A48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EMEND (aprépitant) 125 mg / 80 mg</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 gélule de 125 mg à J1 de la chimiothérapie, puis 1 gélule de 80 mg à J2 et à J3</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Antiémétique (anti-NK1)</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FEMARA (létrozole) 2,5 mg</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1 comprimé par jour, à heure fixe, pendant 3 mois</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Hormonothérapie anticancéreuse (anti-aromatase)</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="A49" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ENDOXAN (cyclophosphamide) 50 mg</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">1 comprimé par jour, le matin, avec un grand verre d'eau (chimiothérapie métronomique)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Chimiothérapie orale (agent alkylant)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FENAC (diclofénac) gel</t>
+          <t xml:space="preserve">EOSINE aqueuse 2 %, unidose 2 ml</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 application par jour, le midi</t>
+          <t xml:space="preserve">1 à 2 applications par jour sur les lésions suintantes, à l'aide d'une compresse stérile</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Anti-inflammatoire non stéroïdien local</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Antiseptique asséchant</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FIRMAGON (dégarelix) 120 mg / 80 mg</t>
+          <t xml:space="preserve">EPYCA (prégabaline) 75 mg</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Le 1er mois : 2 injections sous-cutanées de 120 mg ; ensuite : 1 injection sous-cutanée de 80 mg tous les mois</t>
+          <t xml:space="preserve">Au début : 75 mg le soir, puis augmenter progressivement après 3 jours si bonne tolérance à 75 mg matin et soir (soit 150 mg par jour), pendant 1 mois</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Hormonothérapie anticancéreuse (antagoniste de la GnRH)</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Antiépileptique (douleurs neuropathiques)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FLAMMAZINE (sulfadiazine argentique) crème</t>
+          <t xml:space="preserve">ERLEADA (apalutamide) 60 mg</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Étaler 1 fois par jour en couche de 2 à 3 mm sur une peau propre et sèche</t>
+          <t xml:space="preserve">4 comprimés par jour en une seule prise (soit 240 mg par jour)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antibactérien local (brûlures, radiodermite)</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Hormonothérapie anticancéreuse (anti-androgène)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FLUOCARIL gel bifluoré 250 mg</t>
+          <t xml:space="preserve">EUCARBON, comprimé</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Appliquer dans les gouttières fluorées 1 fois par jour, pendant 5 minutes, après le brossage</t>
+          <t xml:space="preserve">1 comprimé matin, midi et soir (soit 3 comprimés par jour), les 2 jours précédant le traitement</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Prévention des caries (fluor)</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Laxatif / adsorbant intestinal (charbon végétal, séné)</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FONTACTIV liquide</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">2 unités par jour (ne remplace pas un repas)</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Complément nutritionnel oral</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="A54" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">FASLODEX (fulvestrant) 250 mg</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">2 injections intramusculaires lentes (1 dans chaque fesse, soit 500 mg) à J1, J15 et J29, puis tous les mois</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Hormonothérapie anticancéreuse (anti-œstrogène)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FONTACTIV poudre</t>
+          <t xml:space="preserve">FAZOL (isoconazole) 2 % crème, 30 g</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4 cuillères-mesures dans 200 ml de liquide (2 cuillères-mesures si lait), 1 à 3 fois par jour (ne remplace pas un repas)</t>
+          <t xml:space="preserve">Appliquer entre les orteils 2 fois par jour pendant 10 jours, puis réévaluer</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Complément nutritionnel oral</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Antifongique local</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FORLAX (macrogol) 10 g</t>
+          <t xml:space="preserve">FEMARA (létrozole) 2,5 mg</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 à 2 sachets par jour, le matin en une prise, en cas de constipation importante</t>
+          <t xml:space="preserve">1 comprimé par jour, à heure fixe, pendant 3 mois</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Laxatif osmotique</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">3 lignes identiques fusionnées.</t>
+          <t xml:space="preserve">Hormonothérapie anticancéreuse (anti-aromatase)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FORTIMEL Protein</t>
+          <t xml:space="preserve">FENAC (diclofénac) gel</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 à 2 compléments par jour (ne remplace pas un repas)</t>
+          <t xml:space="preserve">1 application par jour, le midi</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Complément nutritionnel oral</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Anti-inflammatoire non stéroïdien local</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">FUCIDINE (acide fusidique) crème</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">1 application … fois par jour sur l'infection cutanée, après nettoyage doux et séchage</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Antibiotique local</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">4 lignes fusionnées. Nombre d'applications par jour à préciser.</t>
+      <c r="A58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FIRMAGON (dégarelix) 120 mg / 80 mg</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Le 1er mois : 2 injections sous-cutanées de 120 mg ; ensuite : 1 injection sous-cutanée de 80 mg tous les mois</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Hormonothérapie anticancéreuse (antagoniste de la GnRH)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FUNGIZONE (amphotéricine B) 10 %, suspension buvable</t>
+          <t xml:space="preserve">FLAMMAZINE (sulfadiazine argentique) crème</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2 cuillères à café le matin et 2 le soir (soit 4 cuillères à café par jour) en cas d'infection fongique</t>
+          <t xml:space="preserve">Étaler 1 fois par jour en couche de 2 à 3 mm sur une peau propre et sèche</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antifongique</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">3 lignes : 2 posologies gardées.</t>
+          <t xml:space="preserve">Antibactérien local (brûlures, radiodermite)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FUNGIZONE (amphotéricine B) 10 %, suspension buvable</t>
+          <t xml:space="preserve">FLUOCARIL gel bifluoré 250 mg</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 à 2 cuillères à café matin et soir (soit 2 à 4 cuillères à café par jour)</t>
+          <t xml:space="preserve">Appliquer dans les gouttières fluorées 1 fois par jour, pendant 5 minutes, après le brossage</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antifongique</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Variante.</t>
+          <t xml:space="preserve">Prévention des caries (fluor)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAVISCON</t>
+          <t xml:space="preserve">FONTACTIV liquide</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 dose (tube) avant chaque repas, matin, midi et soir (soit 3 par jour)</t>
+          <t xml:space="preserve">2 unités par jour (ne remplace pas un repas)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Anti-reflux (alginate)</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">2 lignes identiques fusionnées.</t>
+          <t xml:space="preserve">Complément nutritionnel oral</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GEL-LARMES 0,3 %, unidose</t>
+          <t xml:space="preserve">FONTACTIV poudre</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 application dans l'œil toutes les heures en cas de douleur</t>
+          <t xml:space="preserve">4 cuillères-mesures dans 200 ml de liquide (2 cuillères-mesures si lait), 1 à 3 fois par jour (ne remplace pas un repas)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Larmes artificielles (sécheresse oculaire)</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">« dans l'œil » ajouté.</t>
+          <t xml:space="preserve">Complément nutritionnel oral</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GUM HYDRAL gel humectant</t>
+          <t xml:space="preserve">FORLAX (macrogol) 10 g</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4 applications par jour dans la bouche</t>
+          <t xml:space="preserve">1 à 2 sachets par jour, le matin en une prise, en cas de constipation importante</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Substitut salivaire (sécheresse buccale)</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Laxatif osmotique</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEXOMÉDINE (hexamidine)</t>
+          <t xml:space="preserve">FORTIMEL Protein</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2 applications par jour</t>
+          <t xml:space="preserve">1 à 2 compléments par jour (ne remplace pas un repas)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antiseptique local</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Complément nutritionnel oral</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HYALO4 (acide hyaluronique) crème</t>
+          <t xml:space="preserve">FUCIDINE (acide fusidique) crème</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 application en couche fine par jour sur la zone traitée, APRÈS chaque séance de radiothérapie (zone vulvaire : 1 à 2 applications par jour)</t>
+          <t xml:space="preserve">1 application 2 fois par jour sur l'infection cutanée, après nettoyage doux et séchage</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Cicatrisant (soin de la radiodermite)</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">4 lignes : fusionnées en 2 posologies.</t>
+          <t xml:space="preserve">Antibiotique local</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HYALO4 (acide hyaluronique) crème</t>
+          <t xml:space="preserve">FUNGIZONE (amphotéricine B) 10 %, suspension buvable</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 application en couche fine le soir sur le cou (zone traitée), APRÈS la séance de radiothérapie</t>
+          <t xml:space="preserve">2 cuillères à café le matin et 2 le soir (soit 4 cuillères à café par jour) en cas d'infection fongique</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Cicatrisant (soin de la radiodermite)</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Variante ORL.</t>
+          <t xml:space="preserve">Antifongique</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HYDRACORT (hydrocortisone) crème 0,5 %</t>
+          <t xml:space="preserve">GAVISCON</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 application par jour, le midi</t>
+          <t xml:space="preserve">1 dose (tube) avant chaque repas, matin, midi et soir (soit 3 par jour)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Corticoïde local</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Anti-reflux (alginate)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HYDROCORT ou EFFICORT (hydrocortisone) crème</t>
+          <t xml:space="preserve">GEL-LARMES 0,3 %, unidose</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 application le soir sur les boutons</t>
+          <t xml:space="preserve">1 application dans l'œil toutes les heures en cas de douleur</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Corticoïde local</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Larmes artificielles (sécheresse oculaire)</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">HYDROTAC non adhésif (pansement hydrogel) 12,5 x 12,5 cm</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1 pansement par jour</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Dispositif médical (pansement)</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="A69" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">GLIVEC (imatinib) 400 mg</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">1 comprimé par jour, au cours d'un repas, avec un grand verre d'eau</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Thérapie ciblée (inhibiteur de tyrosine kinase)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">KIT DE DILATATEURS VAGINAUX (4 tailles)</t>
+          <t xml:space="preserve">GUM HYDRAL gel humectant</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Dilatation vaginale progressive (commencer par le plus petit), 2 à 3 fois par semaine, 10 minutes par séance</t>
+          <t xml:space="preserve">4 applications par jour dans la bouche</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Dispositif médical</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Substitut salivaire (sécheresse buccale)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">KLEAN PREP</t>
+          <t xml:space="preserve">HEXOMÉDINE (hexamidine)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4 sachets dans 4 litres d'eau : 2 litres entre 18 h et 20 h la veille, puis 2 litres entre 0 h et 2 h le jour de l'examen</t>
+          <t xml:space="preserve">2 applications par jour</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Préparation colique (laxatif osmotique)</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Antiseptique local</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LIXIFOR, gélule</t>
+          <t xml:space="preserve">HYALO4 (acide hyaluronique) crème</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 gélule le soir au coucher avec un grand verre d'eau, en cas de constipation importante</t>
+          <t xml:space="preserve">1 application en couche fine par jour sur la zone traitée, APRÈS chaque séance de radiothérapie (zone vulvaire : 1 à 2 applications par jour)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Complément alimentaire (transit intestinal, plantes)</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">3 lignes identiques fusionnées.</t>
+          <t xml:space="preserve">Cicatrisant (soin de la radiodermite)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LOMEXINE (fenticonazole) 2 % crème vulvaire</t>
+          <t xml:space="preserve">HYDRACORT (hydrocortisone) crème 0,5 %</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 application matin et soir (soit 2 par jour) pendant 1 semaine</t>
+          <t xml:space="preserve">1 application par jour, le midi</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antifongique local</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">2 lignes identiques fusionnées.</t>
+          <t xml:space="preserve">Corticoïde local</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LOMEXINE (fenticonazole) 600 mg ovule</t>
+          <t xml:space="preserve">HYDROCORT ou EFFICORT (hydrocortisone) crème</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 ovule le soir au coucher, en une seule fois (dose unique)</t>
+          <t xml:space="preserve">1 application le soir sur les boutons</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antifongique gynécologique</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">2 lignes identiques fusionnées.</t>
+          <t xml:space="preserve">Corticoïde local</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LOPERIUM (lopéramide) 2 mg</t>
+          <t xml:space="preserve">HYDROTAC non adhésif (pansement hydrogel) 12,5 x 12,5 cm</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 à 2 comprimés en cas de diarrhée importante, maximum 6 comprimés par jour</t>
+          <t xml:space="preserve">1 pansement par jour</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antidiarrhéique</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">4 lignes identiques fusionnées.</t>
+          <t xml:space="preserve">Dispositif médical (pansement)</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LYRICA (prégabaline) 50 mg</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1 comprimé matin et soir (soit 2 comprimés = 100 mg par jour) pour commencer</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Antiépileptique (douleurs neuropathiques)</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">6 lignes : 2 posologies gardées.</t>
+      <c r="A76" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">IBRANCE (palbociclib) 125 mg</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">1 par jour, à heure fixe, au cours d'un repas, pendant 21 jours, puis 7 jours d'arrêt (cycle de 28 jours), avec l'hormonothérapie</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Thérapie ciblée (inhibiteur de CDK4/6)</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LYRICA (prégabaline) 50 mg</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1 comprimé matin et soir (soit 2 comprimés = 100 mg par jour) pendant 1 mois</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Antiépileptique (douleurs neuropathiques)</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Variante.</t>
+      <c r="A77" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">KEPPRA (lévétiracétam) 500 mg</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">1 comprimé matin et soir (soit 2 comprimés par jour)</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Antiépileptique</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MAGMINE (magnésium + vitamine B6)</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1 comprimé le matin</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Supplément en magnésium</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="A78" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">KISQALI (ribociclib) 200 mg</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">3 comprimés (600 mg) en une prise par jour, à heure fixe, pendant 21 jours, puis 7 jours d'arrêt (cycle de 28 jours), avec l'hormonothérapie</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Thérapie ciblée (inhibiteur de CDK4/6)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MEPILEX EM / TRANSFER (pansement hydrocellulaire)</t>
+          <t xml:space="preserve">KIT DE DILATATEURS VAGINAUX (4 tailles)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 pansement, à changer tous les jours après nettoyage soigneux</t>
+          <t xml:space="preserve">Dilatation vaginale progressive (commencer par le plus petit), 2 à 3 fois par semaine, 10 minutes par séance</t>
         </is>
       </c>
       <c r="C79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Dispositif médical (pansement)</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Dispositif médical</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MORIDIL pommade</t>
+          <t xml:space="preserve">KLEAN PREP</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 application 2 fois par jour (matin et soir) sur la zone anale</t>
+          <t xml:space="preserve">4 sachets dans 4 litres d'eau : 2 litres entre 18 h et 20 h la veille, puis 2 litres entre 0 h et 2 h le jour de l'examen</t>
         </is>
       </c>
       <c r="C80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antihémorroïdaire (lidocaïne)</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Vous aviez écrit « MORIDILE crème » : MORIDIL pommade au Maroc.</t>
+          <t xml:space="preserve">Préparation colique (laxatif osmotique)</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MORIDIL suppositoire</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1 suppositoire enduit de pommade, 2 fois par jour</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Antihémorroïdaire (lidocaïne)</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="A81" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">LEVOTHYROX (lévothyroxine) 25 / 50 / 100 µg</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">1 comprimé le matin à jeun, 30 minutes avant le petit-déjeuner</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Hormone thyroïdienne</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOSCONTIN LP (sulfate de morphine) 10 / 30 / 60 / 100 mg</t>
+          <t xml:space="preserve">LIXIFOR, gélule</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé le matin et 1 le soir (toutes les 12 heures)</t>
+          <t xml:space="preserve">1 gélule le soir au coucher avec un grand verre d'eau</t>
         </is>
       </c>
       <c r="C82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antalgique de palier 3 (morphine à libération prolongée)</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">« toutes les 12 heures » ajouté.</t>
+          <t xml:space="preserve">Complément alimentaire (transit intestinal, plantes)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTILIUM (dompéridone) sirop</t>
+          <t xml:space="preserve">LOMEXINE (fenticonazole) 2 % crème vulvaire</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 cuillère-mesure 3 fois par jour, 15 minutes avant les repas, pendant 3 jours</t>
+          <t xml:space="preserve">1 application matin et soir (soit 2 par jour) pendant 1 semaine</t>
         </is>
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antiémétique (antidopaminergique)</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Antifongique local</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOVICOL (macrogol)</t>
+          <t xml:space="preserve">LOMEXINE (fenticonazole) 600 mg ovule</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 sachet matin et soir (soit 2 sachets par jour) en cas de constipation importante</t>
+          <t xml:space="preserve">1 ovule le soir au coucher, en une seule fois (dose unique)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Laxatif osmotique</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">3 lignes identiques fusionnées.</t>
+          <t xml:space="preserve">Antifongique gynécologique</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">MYCODERME pommade</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">1 application 2 fois par jour (matin et soir) pendant 3 semaines</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Antifongique local</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Classe à vérifier.</t>
+      <c r="A85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">LOPERIUM (lopéramide) 2 mg</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 à 2 comprimés en cas de diarrhée importante, maximum 6 comprimés par jour</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Antidiarrhéique</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">NEUPOGEN (filgrastim) 48 MU</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1 injection sous-cutanée par jour pendant 5 jours (de J2 à J6 après la chimiothérapie)</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Facteur de croissance (G-CSF)</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="A86" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">LOVENOX (énoxaparine) 4 000 UI / 0,4 ml</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">1 injection sous-cutanée par jour pendant … jours</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Anticoagulant (héparine de bas poids moléculaire), prévention</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">NIBIOL FORTE (nitroxoline) 100 mg</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1 comprimé matin, midi et soir (soit 3 comprimés par jour) pendant 10 jours</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Antiseptique urinaire</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="A87" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">LYNPARZA (olaparib) 150 mg</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">2 comprimés matin et soir (soit 4 comprimés = 600 mg par jour), en continu</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Thérapie ciblée (inhibiteur de PARP)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NIVESTIM (filgrastim) 30 MU</t>
+          <t xml:space="preserve">LYRICA (prégabaline) 50 mg</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 injection sous-cutanée par jour pendant 3 jours (de J2 à J4 après la chimiothérapie)</t>
+          <t xml:space="preserve">1 comprimé matin et soir (soit 2 comprimés = 100 mg par jour) pour commencer</t>
         </is>
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Facteur de croissance (G-CSF)</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Antiépileptique (douleurs neuropathiques)</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">NOCAND 50 mg</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">1 comprimé le matin pendant 7 jours</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Médicament introuvable sur les sites marocains (fluconazole ?) : nom et classe à vérifier.</t>
+      <c r="A89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">MAGMINE (magnésium + vitamine B6)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 comprimé le matin</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Supplément en magnésium</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NORMACOL lavement</t>
+          <t xml:space="preserve">MEPILEX EM / TRANSFER (pansement hydrocellulaire)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 lavement en l'absence de selles pendant 3 jours malgré les autres traitements (MOVICOL…)</t>
+          <t xml:space="preserve">1 pansement, à changer tous les jours après nettoyage soigneux</t>
         </is>
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Laxatif (lavement rectal)</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">4 lignes fusionnées.</t>
+          <t xml:space="preserve">Dispositif médical (pansement)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">OEDES (oméprazole) 20 mg</t>
+          <t xml:space="preserve">MORIDIL pommade</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 gélule le matin</t>
+          <t xml:space="preserve">1 application 2 fois par jour (matin et soir) sur la zone anale</t>
         </is>
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antiulcéreux (inhibiteur de la pompe à protons)</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">6 lignes : 3 posologies gardées. OEDES se présente en gélules.</t>
+          <t xml:space="preserve">Antihémorroïdaire (lidocaïne)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">OEDES (oméprazole) 20 mg</t>
+          <t xml:space="preserve">MORIDIL suppositoire</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 gélule le matin, à arrêter en même temps que le COTIPRED</t>
+          <t xml:space="preserve">1 suppositoire enduit de pommade, 2 fois par jour</t>
         </is>
       </c>
       <c r="C92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antiulcéreux (inhibiteur de la pompe à protons)</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Variante.</t>
+          <t xml:space="preserve">Antihémorroïdaire (lidocaïne)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">OEDES (oméprazole) 20 mg</t>
+          <t xml:space="preserve">MOSCONTIN LP (sulfate de morphine) 10 / 30 / 60 / 100 mg</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 gélule le matin à J1, J2 et J3 après la chimiothérapie</t>
+          <t xml:space="preserve">1 comprimé le matin et 1 le soir (toutes les 12 heures)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antiulcéreux (inhibiteur de la pompe à protons)</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Variante.</t>
+          <t xml:space="preserve">Antalgique de palier 3 (morphine à libération prolongée)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">OFLOCET (ofloxacine) 200 mg</t>
+          <t xml:space="preserve">MOTILIUM (dompéridone) sirop</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé (200 mg) par jour pendant 5 jours</t>
+          <t xml:space="preserve">1 cuillère-mesure 3 fois par jour, 15 minutes avant les repas, pendant 3 jours</t>
         </is>
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antibiotique (fluoroquinolone)</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Antiémétique (antidopaminergique)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">OMIX (tamsulosine) 0,4 mg</t>
+          <t xml:space="preserve">MOVICOL (macrogol)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé le soir</t>
+          <t xml:space="preserve">1 sachet matin et soir (soit 2 sachets par jour) en cas de constipation importante</t>
         </is>
       </c>
       <c r="C95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Alpha-bloquant (troubles urinaires)</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Laxatif osmotique</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ORGOVYX (rélugolix) 120 mg</t>
+          <t xml:space="preserve">MYCODERME pommade</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3 comprimés le 1er jour, puis 1 comprimé par jour</t>
+          <t xml:space="preserve">1 application 2 fois par jour (matin et soir) pendant 3 semaines</t>
         </is>
       </c>
       <c r="C96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Hormonothérapie anticancéreuse (antagoniste de la GnRH)</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Antifongique local</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">OROCAL VITAMINE D3 500 mg / 400 UI</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1 comprimé matin et soir (soit 2 comprimés par jour)</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Calcium + vitamine D</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="A97" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">NAVELBINE (vinorelbine) 20 mg / 30 mg, capsule molle</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">… capsules de 20 mg et … capsules de 30 mg en une prise, 1 fois par semaine (60 à 80 mg/m²), au cours d'un repas léger, avalées entières avec un verre d'eau, sans les mâcher</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Chimiothérapie orale (vinca-alcaloïde)</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">PARACÉTAMOL 1 g</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1 comprimé en cas de douleur, maximum 4 comprimés par jour (au moins 4 heures entre 2 prises)</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Antalgique et antipyrétique (palier 1)</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">6 lignes fusionnées (2 disaient « maximum 3 à 4 »). Intervalle de 4 heures ajouté.</t>
+      <c r="A98" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">NEULASTIM (pegfilgrastim) 6 mg</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">1 injection sous-cutanée par cycle, 24 heures après la fin de la chimiothérapie (J2)</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Facteur de croissance (G-CSF à action prolongée)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PARACÉTAMOL CODÉINÉ</t>
+          <t xml:space="preserve">NEUPOGEN (filgrastim) 48 MU</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé en cas de douleur, maximum 4 comprimés par jour</t>
+          <t xml:space="preserve">1 injection sous-cutanée par jour pendant 5 jours (de J2 à J6 après la chimiothérapie)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antalgique de palier 2 (paracétamol + codéine)</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">6 lignes identiques fusionnées.</t>
+          <t xml:space="preserve">Facteur de croissance (G-CSF)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PENTASA (mésalazine) 1 g / 100 ml, suspension rectale</t>
+          <t xml:space="preserve">NIBIOL FORTE (nitroxoline) 100 mg</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 lavement par jour, allongé sur le côté, pendant 2 semaines, puis selon les symptômes</t>
+          <t xml:space="preserve">1 comprimé matin, midi et soir (soit 3 comprimés par jour) pendant 10 jours</t>
         </is>
       </c>
       <c r="C100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Anti-inflammatoire intestinal (rectite)</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">2 lignes identiques fusionnées.</t>
+          <t xml:space="preserve">Antiseptique urinaire</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PENTASA (mésalazine) 1 g, suppositoire</t>
+          <t xml:space="preserve">NIVESTIM (filgrastim) 30 MU</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 suppositoire le soir pendant 7 jours</t>
+          <t xml:space="preserve">1 injection sous-cutanée par jour pendant 3 jours (de J2 à J4 après la chimiothérapie)</t>
         </is>
       </c>
       <c r="C101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Anti-inflammatoire intestinal (rectite)</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Facteur de croissance (G-CSF)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PRIMPERAN (métoclopramide) 10 mg</t>
+          <t xml:space="preserve">NOCAND 50 mg</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé matin, midi et soir (soit 3 comprimés par jour) en cas de nausées</t>
+          <t xml:space="preserve">1 comprimé le matin pendant 7 jours</t>
         </is>
       </c>
       <c r="C102" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Antiémétique (antidopaminergique)</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -2333,1016 +1822,1041 @@
     <row r="103">
       <c r="A103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PYOSTACINE (pristinamycine) 500 mg</t>
+          <t xml:space="preserve">NORMACOL lavement</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2 comprimés matin et soir (soit 4 comprimés = 2 g par jour) pendant 8 à 14 jours</t>
+          <t xml:space="preserve">1 lavement en l'absence de selles pendant 3 jours malgré les autres traitements (MOVICOL…)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antibiotique (synergistine)</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Laxatif (lavement rectal)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RECTOLAX ou ZETALAX, lavement</t>
+          <t xml:space="preserve">OEDES (oméprazole) 20 mg</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 lavement en cas de constipation légère</t>
+          <t xml:space="preserve">1 gélule le matin</t>
         </is>
       </c>
       <c r="C104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Laxatif (lavement rectal)</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Lignes RECTOLAX / ZETALAX regroupées en 3 posologies.</t>
+          <t xml:space="preserve">Antiulcéreux (inhibiteur de la pompe à protons)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RECTOLAX ou ZETALAX, lavement</t>
+          <t xml:space="preserve">OFLOCET (ofloxacine) 200 mg</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 lavement avant chaque séance de radiothérapie (quantité : au moins 10 lavements)</t>
+          <t xml:space="preserve">1 comprimé (200 mg) par jour pendant 5 jours</t>
         </is>
       </c>
       <c r="C105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Laxatif (lavement rectal)</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Variante. « en donner au moins 10 » = quantité à délivrer.</t>
+          <t xml:space="preserve">Antibiotique (fluoroquinolone)</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">SCOPODERM (scopolamine) 1 mg / 72 h</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1 patch derrière l'oreille, à changer toutes les 72 heures (garder 3 jours), pendant 1 mois</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Anticholinergique (antiémétique, anti-sécrétoire)</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="A106" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">OLANZAPINE (ZYPREXA) 5 mg</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">1 comprimé le soir, de J1 à J4 de la chimiothérapie</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Antiémétique (neuroleptique)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SEDASTERIL crème lavante PM</t>
+          <t xml:space="preserve">OMIX (tamsulosine) 0,4 mg</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pour la toilette intime, chaque jour</t>
+          <t xml:space="preserve">1 comprimé le soir</t>
         </is>
       </c>
       <c r="C107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Hygiène intime</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Alpha-bloquant (troubles urinaires)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SEDASTERIL gel lubrifiant</t>
+          <t xml:space="preserve">ORGOVYX (rélugolix) 120 mg</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 à 2 applications par jour sur la zone vulvaire, ou avant les rapports sexuels</t>
+          <t xml:space="preserve">3 comprimés le 1er jour, puis 1 comprimé par jour</t>
         </is>
       </c>
       <c r="C108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Lubrifiant intime</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">2 lignes identiques fusionnées.</t>
+          <t xml:space="preserve">Hormonothérapie anticancéreuse (antagoniste de la GnRH)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SEVREDOL (sulfate de morphine) 10 mg</t>
+          <t xml:space="preserve">OROCAL VITAMINE D3 500 mg / 400 UI</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé en cas de pic de douleur, maximum 6 comprimés par jour (au moins 1 heure entre 2 prises)</t>
+          <t xml:space="preserve">1 comprimé matin et soir (soit 2 comprimés par jour)</t>
         </is>
       </c>
       <c r="C109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antalgique de palier 3 (morphine à libération immédiate)</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Calcium + vitamine D</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SMECTA (diosmectite) 3 g</t>
+          <t xml:space="preserve">PARACÉTAMOL 1 g</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 à 2 sachets en cas de diarrhée légère, maximum 6 sachets par jour</t>
+          <t xml:space="preserve">1 comprimé en cas de douleur, maximum 4 comprimés par jour (au moins 4 heures entre 2 prises)</t>
         </is>
       </c>
       <c r="C110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antidiarrhéique</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">4 lignes identiques fusionnées.</t>
+          <t xml:space="preserve">Antalgique et antipyrétique (palier 1)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SPASFON LYOC (phloroglucinol)</t>
+          <t xml:space="preserve">PARACÉTAMOL CODÉINÉ</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 à 2 comprimés en cas de douleurs abdominales, maximum 6 comprimés par jour</t>
+          <t xml:space="preserve">1 comprimé en cas de douleur, maximum 4 comprimés par jour</t>
         </is>
       </c>
       <c r="C111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antispasmodique</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">4 lignes identiques fusionnées.</t>
+          <t xml:space="preserve">Antalgique de palier 2 (paracétamol + codéine)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SYMBICORT TURBUHALER (budésonide + formotérol) 200 / 6 µg</t>
+          <t xml:space="preserve">PENTASA (mésalazine) 1 g / 100 ml, suspension rectale</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 inhalation matin et soir (soit 2 inhalations par jour) pendant 1 mois</t>
+          <t xml:space="preserve">1 lavement par jour, allongé sur le côté, pendant 2 semaines, puis selon les symptômes</t>
         </is>
       </c>
       <c r="C112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antiasthmatique (corticoïde + bronchodilatateur)</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Anti-inflammatoire intestinal (rectite)</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">SYSMETIX, gélule</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">1 gélule par jour</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Introuvable comme médicament (peut-être le complément SYMETIX) : nom et classe à vérifier.</t>
+      <c r="A113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PENTASA (mésalazine) 1 g, suppositoire</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 suppositoire le soir pendant 7 jours</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Anti-inflammatoire intestinal (rectite)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TADALAFIL 10 mg</t>
+          <t xml:space="preserve">PRIMPERAN (métoclopramide) 10 mg</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé au moins 30 minutes avant l'activité sexuelle (maximum 1 par jour), pendant 3 mois</t>
+          <t xml:space="preserve">1 comprimé matin, midi et soir (soit 3 comprimés par jour) en cas de nausées</t>
         </is>
       </c>
       <c r="C114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Traitement de la dysfonction érectile (inhibiteur de la PDE5)</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Antiémétique (antidopaminergique)</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">TADALAFIL 20 mg</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1 comprimé au moins 30 minutes avant l'activité sexuelle (maximum 1 par jour), pendant 3 mois</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Traitement de la dysfonction érectile (inhibiteur de la PDE5)</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="A115" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">PROLIA (dénosumab) 60 mg</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">1 injection sous-cutanée tous les 6 mois, avec calcium et vitamine D</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Anti-résorptif osseux (ostéoporose sous hormonothérapie)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TADALAFIL 5 mg</t>
+          <t xml:space="preserve">PYOSTACINE (pristinamycine) 500 mg</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé par jour, le matin, pendant 3 mois</t>
+          <t xml:space="preserve">2 comprimés matin et soir (soit 4 comprimés = 2 g par jour) pendant 8 à 14 jours</t>
         </is>
       </c>
       <c r="C116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Traitement de la dysfonction érectile (inhibiteur de la PDE5)</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Antibiotique (synergistine)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TAMOXIFÈNE 20 mg</t>
+          <t xml:space="preserve">RECTOLAX microlavement</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé par jour, à heure fixe, pendant 3 mois</t>
+          <t xml:space="preserve">1 lavement avant chaque séance de radiothérapie (quantité : au moins 10 lavements)</t>
         </is>
       </c>
       <c r="C117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Hormonothérapie anticancéreuse (anti-œstrogène)</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Laxatif (lavement rectal)</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">TANGANIL B20, comprimé</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">1 comprimé matin, midi et soir (soit 3 comprimés par jour) pendant 1 mois</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Antivertigineux (acétylleucine)</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">« B20 » à vérifier (TANGANIL = acétylleucine 500 mg).</t>
+      <c r="A118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOPODERM (scopolamine) 1 mg / 72 h</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 patch derrière l'oreille, à changer toutes les 72 heures (garder 3 jours), pendant 1 mois</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Anticholinergique (antiémétique, anti-sécrétoire)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TAVANIC (lévofloxacine) 500 mg</t>
+          <t xml:space="preserve">SEDASTERIL crème lavante PM</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé (500 mg) le 1er jour, puis ½ comprimé (250 mg) par jour pendant 5 jours</t>
+          <t xml:space="preserve">Pour la toilette intime, chaque jour</t>
         </is>
       </c>
       <c r="C119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antibiotique (fluoroquinolone)</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Hygiène intime</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">TEGUMA (terbinafine) 250 mg</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">2 applications par jour</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Antifongique</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Incohérence : TEGUMA 250 mg est un comprimé ; pour des applications, c'est TEGUMA 1 % crème. À corriger.</t>
+      <c r="A120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SEDASTERIL gel lubrifiant</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 à 2 applications par jour sur la zone vulvaire, ou avant les rapports sexuels</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Lubrifiant intime</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TEMODAL (témozolomide) 75 mg/m²/jour</t>
+          <t xml:space="preserve">SEVREDOL (sulfate de morphine) 10 mg</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 prise par jour, à jeun, 1 h 30 avant la radiothérapie, tous les jours du début à la fin de la radiothérapie</t>
+          <t xml:space="preserve">1 comprimé en cas de pic de douleur, maximum 6 comprimés par jour (au moins 1 heure entre 2 prises)</t>
         </is>
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Chimiothérapie orale (agent alkylant)</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Antalgique de palier 3 (morphine à libération immédiate)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TIORFAN (racécadotril) 100 mg</t>
+          <t xml:space="preserve">SMECTA (diosmectite) 3 g</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 à 2 gélules si les diarrhées importantes persistent sous LOPERIUM, maximum 6 gélules par jour</t>
+          <t xml:space="preserve">1 à 2 sachets en cas de diarrhée légère, maximum 6 sachets par jour</t>
         </is>
       </c>
       <c r="C122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antidiarrhéique (anti-sécrétoire)</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">3 lignes fusionnées. TIORFAN 100 mg se présente en gélules.</t>
+          <t xml:space="preserve">Antidiarrhéique</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TITANORÉINE à la lidocaïne 2 % crème</t>
+          <t xml:space="preserve">SPASFON LYOC (phloroglucinol)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 application avant et après chaque selle, maximum 4 applications par jour</t>
+          <t xml:space="preserve">1 à 2 comprimés en cas de douleurs abdominales, maximum 6 comprimés par jour</t>
         </is>
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antihémorroïdaire</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">3 lignes identiques fusionnées.</t>
+          <t xml:space="preserve">Antispasmodique</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">TITANORÉINE suppositoire</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1 à 2 suppositoires par jour jusqu'à cicatrisation</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Antihémorroïdaire</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">3 lignes identiques fusionnées.</t>
+      <c r="A124" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">SULFARLEM S 25 (anétholtrithione)</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">1 comprimé matin, midi et soir (soit 3 comprimés par jour), avant les repas</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Sialagogue (sécheresse buccale)</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TOLÉRIANE crème légère</t>
+          <t xml:space="preserve">SYMBICORT TURBUHALER (budésonide + formotérol) 200 / 6 µg</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 application par jour, le matin</t>
+          <t xml:space="preserve">1 inhalation matin et soir (soit 2 inhalations par jour) pendant 1 mois</t>
         </is>
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Soin dermatologique apaisant</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Antiasthmatique (corticoïde + bronchodilatateur)</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">TRAMAL (tramadol) 50 mg</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">1 comprimé en cas de pic de douleur, maximum 4 comprimés par jour</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Antalgique de palier 2 (tramadol)</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">3 lignes : 2 posologies différentes gardées (maximum 4 ou 6 par jour), à choisir.</t>
+      <c r="A126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TADALAFIL 10 mg</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 comprimé au moins 30 minutes avant l'activité sexuelle (maximum 1 par jour), pendant 3 mois</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Traitement de la dysfonction érectile (inhibiteur de la PDE5)</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">TRAMAL (tramadol) 50 mg</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">1 comprimé en cas de douleur, maximum 6 comprimés par jour (au moins 4 heures entre 2 prises)</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Antalgique de palier 2 (tramadol)</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Variante.</t>
+      <c r="A127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TADALAFIL 20 mg</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 comprimé au moins 30 minutes avant l'activité sexuelle (maximum 1 par jour), pendant 3 mois</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Traitement de la dysfonction érectile (inhibiteur de la PDE5)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TRAMAL LP (tramadol) 100 mg</t>
+          <t xml:space="preserve">TADALAFIL 5 mg</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé le matin et 1 le soir (toutes les 12 heures)</t>
+          <t xml:space="preserve">1 comprimé par jour, le matin, pendant 3 mois</t>
         </is>
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antalgique de palier 2 (tramadol à libération prolongée)</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">3 lignes fusionnées (« TRAMAL 100 mg » et « TRAMAL 100 mg LP »).</t>
+          <t xml:space="preserve">Traitement de la dysfonction érectile (inhibiteur de la PDE5)</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">UROREC (silodosine) 4 mg</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1 gélule le soir pendant 3 mois</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Alpha-bloquant (troubles urinaires)</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="A129" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">TAGRISSO (osimertinib) 80 mg</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">1 comprimé par jour, à heure fixe, pendant ou en dehors des repas</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Thérapie ciblée (inhibiteur de l'EGFR)</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UROREC (silodosine) 8 mg</t>
+          <t xml:space="preserve">TAMOXIFÈNE 20 mg</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 gélule le soir pendant 3 mois</t>
+          <t xml:space="preserve">1 comprimé par jour, à heure fixe, pendant 3 mois</t>
         </is>
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Alpha-bloquant (troubles urinaires)</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Hormonothérapie anticancéreuse (anti-œstrogène)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UVEDOSE 100 000 UI, solution buvable</t>
+          <t xml:space="preserve">TANGANIL B20, comprimé</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 ampoule par mois à boire sur un sucre pendant 2 mois, puis 1 ampoule tous les 3 mois</t>
+          <t xml:space="preserve">1 comprimé matin, midi et soir (soit 3 comprimés par jour) pendant 1 mois</t>
         </is>
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Vitamine D</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Antivertigineux (acétylleucine)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VASELINE stérile</t>
+          <t xml:space="preserve">TAVANIC (lévofloxacine) 500 mg</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 à 2 applications par jour, en couche épaisse, sur les lésions suintantes et croûteuses</t>
+          <t xml:space="preserve">1 comprimé (500 mg) le 1er jour, puis ½ comprimé (250 mg) par jour pendant 5 jours</t>
         </is>
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Émollient</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">3 lignes identiques fusionnées.</t>
+          <t xml:space="preserve">Antibiotique (fluoroquinolone)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VECA (solifénacine) 10 mg</t>
+          <t xml:space="preserve">TEGUMA (terbinafine) 250 mg</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé le soir pendant 1 mois en cas de brûlures mictionnelles</t>
+          <t xml:space="preserve">1 comprimé matin et soir soit 2 comprimés par jour</t>
         </is>
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antispasmodique urinaire (anticholinergique)</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Antifongique</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VECA (solifénacine) 5 mg</t>
+          <t xml:space="preserve">TEMODAL (témozolomide) 75 mg/m²/jour</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé le soir pendant 1 mois en cas de brûlures mictionnelles</t>
+          <t xml:space="preserve">1 prise par jour, à jeun, 1 h 30 avant la radiothérapie, tous les jours du début à la fin de la radiothérapie</t>
         </is>
       </c>
       <c r="C134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antispasmodique urinaire (anticholinergique)</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Chimiothérapie orale (agent alkylant)</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">VENTOLINE (salbutamol) 2,5 mg / 2,5 ml, solution pour nébuliseur</t>
+          <t xml:space="preserve">TEMODAL (témozolomide), phase adjuvante</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">1 nébulisation en cas de difficulté respiratoire, maximum 4 par jour</t>
+          <t xml:space="preserve">1 prise par jour, à jeun, 5 jours de suite (J1 à J5) tous les 28 jours : 150 mg/m² par jour au 1er cycle, puis 200 mg/m² par jour si bonne tolérance (gélules de … mg)</t>
         </is>
       </c>
       <c r="C135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">Bronchodilatateur (bêta-2 agoniste)</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Vous aviez écrit « 1 bouffée » : avec un nébuliseur, c'est une nébulisation. À vérifier.</t>
+          <t xml:space="preserve">Chimiothérapie orale (agent alkylant)</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">VITAMINE A 25 000 UI</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">1 application matin et soir (soit 2 par jour) pendant 1 mois</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Cicatrisant (vitamine A)</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Forme (pommade ?) et classe à vérifier.</t>
+      <c r="A136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TIORFAN (racécadotril) 100 mg</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 à 2 gélules si les diarrhées importantes persistent sous LOPERIUM, maximum 6 gélules par jour</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Antidiarrhéique (anti-sécrétoire)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VITANEVRIL FORTE</t>
+          <t xml:space="preserve">TITANORÉINE à la lidocaïne 2 % crème</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé matin et soir (soit 2 comprimés par jour) pendant 3 mois</t>
+          <t xml:space="preserve">1 application avant et après chaque selle, maximum 4 applications par jour</t>
         </is>
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Vitamines B (neurotropes)</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Antihémorroïdaire</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">XATRAL LP (alfuzosine) 10 mg</t>
+          <t xml:space="preserve">TITANORÉINE suppositoire</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé par jour, après le repas du soir</t>
+          <t xml:space="preserve">1 à 2 suppositoires par jour jusqu'à cicatrisation</t>
         </is>
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Alpha-bloquant (troubles urinaires)</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">2 lignes identiques fusionnées.</t>
+          <t xml:space="preserve">Antihémorroïdaire</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">XTANDI (enzalutamide) 40 mg</t>
+          <t xml:space="preserve">TOLÉRIANE crème légère</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4 comprimés par jour en une seule prise le matin (soit 160 mg par jour)</t>
+          <t xml:space="preserve">1 application par jour, le matin</t>
         </is>
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Hormonothérapie anticancéreuse (anti-androgène)</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Soin dermatologique apaisant</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">XYLITOL chewing-gum</t>
+          <t xml:space="preserve">TRAMAL (tramadol) 50 mg</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">À mâcher selon les besoins, jusqu'à 4 fois par jour</t>
+          <t xml:space="preserve">1 comprimé en cas de douleur, maximum 6 comprimés par jour (au moins 4 heures entre 2 prises)</t>
         </is>
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sécheresse buccale (stimulation salivaire)</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Antalgique de palier 2 (tramadol)</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">XYLOCAÏNE VISQUEUSE (lidocaïne) 2 % gel</t>
+          <t xml:space="preserve">TRAMAL LP (tramadol) 100 mg</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 application dans la bouche sur les zones douloureuses, après les repas ou au moins 1 heure avant</t>
+          <t xml:space="preserve">1 comprimé le matin et 1 comprimé le soir (toutes les 12 heures)</t>
         </is>
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Anesthésique local</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">4 lignes : 2 posologies gardées.</t>
+          <t xml:space="preserve">Antalgique de palier 2 (tramadol à libération prolongée)</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">XYLOCAÏNE VISQUEUSE (lidocaïne) 2 % gel</t>
+          <t xml:space="preserve">UROREC (silodosine) 4 mg</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Application locale avant la dilatation vaginale ou sur les zones douloureuses</t>
+          <t xml:space="preserve">1 gélule le soir pendant 3 mois</t>
         </is>
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Anesthésique local</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Variante gynécologique.</t>
+          <t xml:space="preserve">Alpha-bloquant (troubles urinaires)</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">YOFOLVIT (acide folique)</t>
+          <t xml:space="preserve">UROREC (silodosine) 8 mg</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé par jour, le matin, pendant 3 mois</t>
+          <t xml:space="preserve">1 gélule le soir pendant 3 mois</t>
         </is>
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Vitamine B9 (acide folique)</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Alpha-bloquant (troubles urinaires)</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ZETALAX, microlavement</t>
+          <t xml:space="preserve">UVEDOSE 100 000 UI, solution buvable</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 lavement le matin, la veille et le jour du traitement</t>
+          <t xml:space="preserve">1 ampoule par mois à boire sur un sucre pendant 2 mois, puis 1 ampoule tous les 3 mois</t>
         </is>
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Laxatif (lavement rectal)</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Variante.</t>
+          <t xml:space="preserve">Vitamine D</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ZOLADEX LP (goséréline) 10,8 mg</t>
+          <t xml:space="preserve">VASELINE stérile</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 injection sous-cutanée tous les 3 mois</t>
+          <t xml:space="preserve">1 à 2 applications par jour, en couche épaisse, sur les lésions suintantes et croûteuses</t>
         </is>
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Hormonothérapie anticancéreuse (agoniste de la LH-RH)</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Émollient</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ZOPHREN (ondansétron) 8 mg</t>
+          <t xml:space="preserve">VECA (solifénacine) 10 mg</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé matin et soir (soit 2 comprimés par jour) à J1, J2 et J3 après la chimiothérapie (pendant 3 jours)</t>
+          <t xml:space="preserve">1 comprimé le soir pendant 1 mois en cas de brûlures mictionnelles</t>
         </is>
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antiémétique (sétron, anti-5HT3)</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">2 posologies gardées.</t>
+          <t xml:space="preserve">Antispasmodique urinaire (anticholinergique)</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ZOPHREN (ondansétron) 8 mg</t>
+          <t xml:space="preserve">VECA (solifénacine) 5 mg</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé si les nausées persistent, maximum 2 comprimés par jour (espacés de 12 heures)</t>
+          <t xml:space="preserve">1 comprimé le soir pendant 1 mois en cas de brûlures mictionnelles</t>
         </is>
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antiémétique (sétron, anti-5HT3)</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Variante.</t>
+          <t xml:space="preserve">Antispasmodique urinaire (anticholinergique)</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">VENTOLINE (salbutamol) 2,5 mg / 2,5 ml, solution pour nébuliseur</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 nébulisation en cas de difficulté respiratoire, maximum 4 par jour</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Bronchodilatateur (bêta-2 agoniste)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">VERZENIOS (abémaciclib) 150 mg</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">1 comprimé matin et soir (soit 300 mg par jour), en continu, avec l'hormonothérapie</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Thérapie ciblée (inhibiteur de CDK4/6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">VITANEVRIL FORTE</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 comprimé matin et soir (soit 2 comprimés par jour) pendant 3 mois</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Vitamines B (neurotropes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">XATRAL LP (alfuzosine) 10 mg</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 comprimé par jour, après le repas du soir</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Alpha-bloquant (troubles urinaires)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">XGEVA (dénosumab) 120 mg</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">1 injection sous-cutanée toutes les 4 semaines, avec calcium et vitamine D</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Anti-résorptif osseux (métastases osseuses)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">XTANDI (enzalutamide) 40 mg</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">4 comprimés par jour en une seule prise le matin (soit 160 mg par jour)</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Hormonothérapie anticancéreuse (anti-androgène)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">XYLITOL chewing-gum</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">À mâcher selon les besoins, jusqu'à 4 fois par jour</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Sécheresse buccale (stimulation salivaire)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">XYLOCAÏNE VISQUEUSE (lidocaïne) 2 % gel</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 application sur les zones douloureuses, après les repas ou au moins 1 heure avant</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Anesthésique local</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">YOFOLVIT (acide folique)</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 comprimé par jour, le matin, pendant 3 mois</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Vitamine B9 (acide folique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ZETALAX, microlavement</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 lavement avant chaque séance de radiothérapie (quantité : au moins 10 lavements)</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Laxatif (lavement rectal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ZOLADEX (goséréline) 3,6 mg</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">1 injection sous-cutanée tous les 28 jours</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Hormonothérapie anticancéreuse (agoniste de la LH-RH)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ZOLADEX LP (goséréline) 10,8 mg</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 injection sous-cutanée tous les 3 mois</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Hormonothérapie anticancéreuse (agoniste de la LH-RH)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ZOMETA (acide zolédronique) 4 mg</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">1 perfusion intraveineuse de 15 minutes toutes les 4 semaines (ou toutes les 12 semaines)</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Bisphosphonate (métastases osseuses)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ZOPHREN (ondansétron) 8 mg</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 comprimé matin et soir (soit 2 comprimés par jour) à J1, J2 et J3 après la chimiothérapie (pendant 3 jours)</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Antiémétique (sétron, anti-5HT3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ZOPHREN (ondansétron) 8 mg</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 comprimé si les nausées persistent, maximum 2 comprimés par jour (espacés de 12 heures)</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Antiémétique (sétron, anti-5HT3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">ZYTIGA (abiratérone) 250 mg</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr" s="2">
+      <c r="B163" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">4 comprimés le matin en une seule prise, à jeun (au moins 2 heures après un repas et 1 heure avant le suivant), avec un grand verre d'eau (soit 1 000 mg par jour)</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr" s="2">
+      <c r="C163" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Hormonothérapie anticancéreuse (inhibiteur de la synthèse des androgènes)</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D148"/>
+  <autoFilter ref="A1:C163"/>
 </worksheet>
 </file>
--- a/listes/Medicaments_Onco360.xlsx
+++ b/listes/Medicaments_Onco360.xlsx
@@ -5,7 +5,7 @@
     <sheet name="Médicaments" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Médicaments!$A$1:$C$163</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Médicaments!$A$1:$C$166</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -24,7 +24,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -34,11 +34,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF3563B0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF3E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -62,15 +57,12 @@
   <cellStyleXfs count="1">
     <xf/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf/>
     <xf fontId="1" fillId="2" borderId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="3" borderId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -171,17 +163,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr" s="3">
+      <c r="A6" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ANDROCUR (cyprotérone) 50 mg</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr" s="3">
+      <c r="B6" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">2 comprimés matin et soir (soit 4 comprimés = 200 mg par jour), à commencer 1 semaine avant la 1re injection d'agoniste de la LH-RH, pendant 3 semaines au total</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr" s="3">
+      <c r="C6" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Hormonothérapie anticancéreuse (anti-androgène)</t>
         </is>
@@ -222,34 +214,34 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr" s="3">
+      <c r="A9" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ARIMIDEX (anastrozole) 1 mg</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr" s="3">
+      <c r="B9" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1 comprimé par jour, à heure fixe, pendant 3 mois</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr" s="3">
+      <c r="C9" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Hormonothérapie anticancéreuse (anti-aromatase)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr" s="3">
+      <c r="A10" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">AROMASINE (exémestane) 25 mg</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr" s="3">
+      <c r="B10" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1 comprimé par jour, après un repas, à heure fixe, pendant 3 mois</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr" s="3">
+      <c r="C10" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Hormonothérapie anticancéreuse (anti-aromatase)</t>
         </is>
@@ -324,17 +316,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr" s="3">
+      <c r="A15" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">BIAFINE émulsion (trolamine)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr" s="3">
+      <c r="B15" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">2 à 3 applications par jour en couche épaisse sur la zone irradiée, à faire pénétrer par un léger massage ; pas d'application dans les 2 heures qui précèdent la séance</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr" s="3">
+      <c r="C15" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Soin de la radiodermite</t>
         </is>
@@ -409,34 +401,34 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr" s="3">
+      <c r="A20" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">CAPÉCITABINE (XELODA) 500 mg / 150 mg</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr" s="3">
+      <c r="B20" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">… comprimés de 500 mg et … comprimés de 150 mg le matin et le soir (… mg/m² 2 fois par jour), dans les 30 minutes qui suivent le repas, de J1 à J14, puis 7 jours d'arrêt (reprise à J22)</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr" s="3">
+      <c r="C20" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Chimiothérapie orale (fluoropyrimidine)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr" s="3">
+      <c r="A21" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">CAPÉCITABINE (XELODA) 500 mg / 150 mg, avec la radiothérapie</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr" s="3">
+      <c r="B21" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">… comprimés de 500 mg et … comprimés de 150 mg le matin et le soir (825 mg/m² 2 fois par jour), dans les 30 minutes qui suivent le repas, chaque jour de radiothérapie</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr" s="3">
+      <c r="C21" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Chimiothérapie orale (fluoropyrimidine)</t>
         </is>
@@ -654,7 +646,7 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 injection tous les 3 mois</t>
+          <t xml:space="preserve">1 injection intramusculaire tous les 3 mois</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
@@ -671,7 +663,7 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 injection tous les 6 mois</t>
+          <t xml:space="preserve">1 injection intramusculaire tous les 6 mois</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
@@ -681,51 +673,51 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr" s="3">
+      <c r="A36" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">DECAPEPTYL LP (triptoréline) 3 mg</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr" s="3">
+      <c r="B36" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1 injection intramusculaire tous les 28 jours</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr" s="3">
+      <c r="C36" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Hormonothérapie anticancéreuse (agoniste de la LH-RH)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr" s="3">
+      <c r="A37" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">DEXAMÉTHASONE 4 mg, comprimé</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr" s="3">
+      <c r="B37" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">2 comprimés le matin (soit 8 mg) à J2 et J3 après la chimiothérapie</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr" s="3">
+      <c r="C37" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Corticoïde (antiémétique)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr" s="3">
+      <c r="A38" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">DEXAMÉTHASONE 4 mg, comprimé (œdème cérébral)</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr" s="3">
+      <c r="B38" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">… comprimés le matin (… mg par jour), puis diminution progressive selon l'évolution</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr" s="3">
+      <c r="C38" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Corticoïde</t>
         </is>
@@ -834,17 +826,17 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr" s="3">
+      <c r="A45" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">DUROGESIC (fentanyl) 12 / 25 / 50 µg/h, patch</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr" s="3">
+      <c r="B45" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1 patch à changer toutes les 72 heures (3 jours)</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr" s="3">
+      <c r="C45" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Antalgique de palier 3 (opioïde transdermique)</t>
         </is>
@@ -902,17 +894,17 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr" s="3">
+      <c r="A49" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ENDOXAN (cyclophosphamide) 50 mg</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr" s="3">
+      <c r="B49" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1 comprimé par jour, le matin, avec un grand verre d'eau (chimiothérapie métronomique)</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr" s="3">
+      <c r="C49" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Chimiothérapie orale (agent alkylant)</t>
         </is>
@@ -987,17 +979,17 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr" s="3">
+      <c r="A54" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FASLODEX (fulvestrant) 250 mg</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr" s="3">
+      <c r="B54" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">2 injections intramusculaires lentes (1 dans chaque fesse, soit 500 mg) à J1, J15 et J29, puis tous les mois</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr" s="3">
+      <c r="C54" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Hormonothérapie anticancéreuse (anti-œstrogène)</t>
         </is>
@@ -1242,17 +1234,17 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr" s="3">
+      <c r="A69" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">GLIVEC (imatinib) 400 mg</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr" s="3">
+      <c r="B69" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1 comprimé par jour, au cours d'un repas, avec un grand verre d'eau</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr" s="3">
+      <c r="C69" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Thérapie ciblée (inhibiteur de tyrosine kinase)</t>
         </is>
@@ -1361,439 +1353,439 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr" s="3">
+      <c r="A76" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">IBRANCE (palbociclib) 125 mg</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr" s="3">
+      <c r="B76" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1 par jour, à heure fixe, au cours d'un repas, pendant 21 jours, puis 7 jours d'arrêt (cycle de 28 jours), avec l'hormonothérapie</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr" s="3">
+      <c r="C76" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Thérapie ciblée (inhibiteur de CDK4/6)</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr" s="3">
+      <c r="A77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">IMFINZI (durvalumab) 500 mg</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">3 flacons de 500 mg (1 500 mg) tous les 28 jours, pendant 12 mois au maximum</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Immunothérapie</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">KEPPRA (lévétiracétam) 500 mg</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr" s="3">
+      <c r="B78" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1 comprimé matin et soir (soit 2 comprimés par jour)</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr" s="3">
+      <c r="C78" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Antiépileptique</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">KISQALI (ribociclib) 200 mg</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">3 comprimés (600 mg) en une prise par jour, à heure fixe, pendant 21 jours, puis 7 jours d'arrêt (cycle de 28 jours), avec l'hormonothérapie</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Thérapie ciblée (inhibiteur de CDK4/6)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">KIT DE DILATATEURS VAGINAUX (4 tailles)</t>
+          <t xml:space="preserve">KEYTRUDA (pembrolizumab) 100 mg</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Dilatation vaginale progressive (commencer par le plus petit), 2 à 3 fois par semaine, 10 minutes par séance</t>
+          <t xml:space="preserve">2 flacons de 100 mg tous les 21 jours</t>
         </is>
       </c>
       <c r="C79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Dispositif médical</t>
+          <t xml:space="preserve">Immunothérapie</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">KLEAN PREP</t>
+          <t xml:space="preserve">KISQALI (ribociclib) 200 mg</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4 sachets dans 4 litres d'eau : 2 litres entre 18 h et 20 h la veille, puis 2 litres entre 0 h et 2 h le jour de l'examen</t>
+          <t xml:space="preserve">3 comprimés (600 mg) en une prise par jour, à heure fixe, pendant 21 jours, puis 7 jours d'arrêt (cycle de 28 jours), avec l'hormonothérapie</t>
         </is>
       </c>
       <c r="C80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Préparation colique (laxatif osmotique)</t>
+          <t xml:space="preserve">Thérapie ciblée (inhibiteur de CDK4/6)</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">LEVOTHYROX (lévothyroxine) 25 / 50 / 100 µg</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">1 comprimé le matin à jeun, 30 minutes avant le petit-déjeuner</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Hormone thyroïdienne</t>
+      <c r="A81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">KIT DE DILATATEURS VAGINAUX (4 tailles)</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Dilatation vaginale progressive (commencer par le plus petit), 2 à 3 fois par semaine, 10 minutes par séance</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Dispositif médical</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LIXIFOR, gélule</t>
+          <t xml:space="preserve">KLEAN PREP</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 gélule le soir au coucher avec un grand verre d'eau</t>
+          <t xml:space="preserve">4 sachets dans 4 litres d'eau : 2 litres entre 18 h et 20 h la veille, puis 2 litres entre 0 h et 2 h le jour de l'examen</t>
         </is>
       </c>
       <c r="C82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Complément alimentaire (transit intestinal, plantes)</t>
+          <t xml:space="preserve">Préparation colique (laxatif osmotique)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LOMEXINE (fenticonazole) 2 % crème vulvaire</t>
+          <t xml:space="preserve">LEVOTHYROX (lévothyroxine) 25 / 50 / 100 µg</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 application matin et soir (soit 2 par jour) pendant 1 semaine</t>
+          <t xml:space="preserve">1 comprimé le matin à jeun, 30 minutes avant le petit-déjeuner</t>
         </is>
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antifongique local</t>
+          <t xml:space="preserve">Hormone thyroïdienne</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LOMEXINE (fenticonazole) 600 mg ovule</t>
+          <t xml:space="preserve">LIXIFOR, gélule</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 ovule le soir au coucher, en une seule fois (dose unique)</t>
+          <t xml:space="preserve">1 gélule le soir au coucher avec un grand verre d'eau</t>
         </is>
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antifongique gynécologique</t>
+          <t xml:space="preserve">Complément alimentaire (transit intestinal, plantes)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">LOMEXINE (fenticonazole) 2 % crème vulvaire</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 application matin et soir (soit 2 par jour) pendant 1 semaine</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Antifongique local</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">LOMEXINE (fenticonazole) 600 mg ovule</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 ovule le soir au coucher, en une seule fois (dose unique)</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Antifongique gynécologique</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LOPERIUM (lopéramide) 2 mg</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr" s="2">
+      <c r="B87" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1 à 2 comprimés en cas de diarrhée importante, maximum 6 comprimés par jour</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr" s="2">
+      <c r="C87" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Antidiarrhéique</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">LOVENOX (énoxaparine) 4 000 UI / 0,4 ml</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">1 injection sous-cutanée par jour pendant … jours</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Anticoagulant (héparine de bas poids moléculaire), prévention</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">LYNPARZA (olaparib) 150 mg</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">2 comprimés matin et soir (soit 4 comprimés = 600 mg par jour), en continu</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Thérapie ciblée (inhibiteur de PARP)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LYRICA (prégabaline) 50 mg</t>
+          <t xml:space="preserve">LOVENOX (énoxaparine) 4 000 UI / 0,4 ml</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé matin et soir (soit 2 comprimés = 100 mg par jour) pour commencer</t>
+          <t xml:space="preserve">1 injection sous-cutanée par jour pendant … jours</t>
         </is>
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antiépileptique (douleurs neuropathiques)</t>
+          <t xml:space="preserve">Anticoagulant (héparine de bas poids moléculaire), prévention</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MAGMINE (magnésium + vitamine B6)</t>
+          <t xml:space="preserve">LYNPARZA (olaparib) 150 mg</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé le matin</t>
+          <t xml:space="preserve">2 comprimés matin et soir (soit 4 comprimés = 600 mg par jour), en continu</t>
         </is>
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Supplément en magnésium</t>
+          <t xml:space="preserve">Thérapie ciblée (inhibiteur de PARP)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MEPILEX EM / TRANSFER (pansement hydrocellulaire)</t>
+          <t xml:space="preserve">LYRICA (prégabaline) 50 mg</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 pansement, à changer tous les jours après nettoyage soigneux</t>
+          <t xml:space="preserve">1 comprimé matin et soir (soit 2 comprimés = 100 mg par jour) pour commencer</t>
         </is>
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Dispositif médical (pansement)</t>
+          <t xml:space="preserve">Antiépileptique (douleurs neuropathiques)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MORIDIL pommade</t>
+          <t xml:space="preserve">MAGMINE (magnésium + vitamine B6)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 application 2 fois par jour (matin et soir) sur la zone anale</t>
+          <t xml:space="preserve">1 comprimé le matin</t>
         </is>
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antihémorroïdaire (lidocaïne)</t>
+          <t xml:space="preserve">Supplément en magnésium</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MORIDIL suppositoire</t>
+          <t xml:space="preserve">MEPILEX EM / TRANSFER (pansement hydrocellulaire)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 suppositoire enduit de pommade, 2 fois par jour</t>
+          <t xml:space="preserve">1 pansement, à changer tous les jours après nettoyage soigneux</t>
         </is>
       </c>
       <c r="C92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antihémorroïdaire (lidocaïne)</t>
+          <t xml:space="preserve">Dispositif médical (pansement)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOSCONTIN LP (sulfate de morphine) 10 / 30 / 60 / 100 mg</t>
+          <t xml:space="preserve">MORIDIL pommade</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé le matin et 1 le soir (toutes les 12 heures)</t>
+          <t xml:space="preserve">1 application 2 fois par jour (matin et soir) sur la zone anale</t>
         </is>
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antalgique de palier 3 (morphine à libération prolongée)</t>
+          <t xml:space="preserve">Antihémorroïdaire (lidocaïne)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTILIUM (dompéridone) sirop</t>
+          <t xml:space="preserve">MORIDIL suppositoire</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 cuillère-mesure 3 fois par jour, 15 minutes avant les repas, pendant 3 jours</t>
+          <t xml:space="preserve">1 suppositoire enduit de pommade, 2 fois par jour</t>
         </is>
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antiémétique (antidopaminergique)</t>
+          <t xml:space="preserve">Antihémorroïdaire (lidocaïne)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOVICOL (macrogol)</t>
+          <t xml:space="preserve">MOSCONTIN LP (sulfate de morphine) 10 / 30 / 60 / 100 mg</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 sachet matin et soir (soit 2 sachets par jour) en cas de constipation importante</t>
+          <t xml:space="preserve">1 comprimé le matin et 1 le soir (toutes les 12 heures)</t>
         </is>
       </c>
       <c r="C95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Laxatif osmotique</t>
+          <t xml:space="preserve">Antalgique de palier 3 (morphine à libération prolongée)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">MOTILIUM (dompéridone) sirop</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 cuillère-mesure 3 fois par jour, 15 minutes avant les repas, pendant 3 jours</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Antiémétique (antidopaminergique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">MOVICOL (macrogol)</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 sachet matin et soir (soit 2 sachets par jour) en cas de constipation importante</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Laxatif osmotique</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">MYCODERME pommade</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr" s="2">
+      <c r="B98" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1 application 2 fois par jour (matin et soir) pendant 3 semaines</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr" s="2">
+      <c r="C98" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Antifongique local</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">NAVELBINE (vinorelbine) 20 mg / 30 mg, capsule molle</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">… capsules de 20 mg et … capsules de 30 mg en une prise, 1 fois par semaine (60 à 80 mg/m²), au cours d'un repas léger, avalées entières avec un verre d'eau, sans les mâcher</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Chimiothérapie orale (vinca-alcaloïde)</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">NEULASTIM (pegfilgrastim) 6 mg</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">1 injection sous-cutanée par cycle, 24 heures après la fin de la chimiothérapie (J2)</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Facteur de croissance (G-CSF à action prolongée)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEUPOGEN (filgrastim) 48 MU</t>
+          <t xml:space="preserve">NAVELBINE (vinorelbine) 20 mg / 30 mg, capsule molle</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 injection sous-cutanée par jour pendant 5 jours (de J2 à J6 après la chimiothérapie)</t>
+          <t xml:space="preserve">… capsules de 20 mg et … capsules de 30 mg en une prise, 1 fois par semaine (60 à 80 mg/m²), au cours d'un repas léger, avalées entières avec un verre d'eau, sans les mâcher</t>
         </is>
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Facteur de croissance (G-CSF)</t>
+          <t xml:space="preserve">Chimiothérapie orale (vinca-alcaloïde)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NIBIOL FORTE (nitroxoline) 100 mg</t>
+          <t xml:space="preserve">NEULASTIM (pegfilgrastim) 6 mg</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé matin, midi et soir (soit 3 comprimés par jour) pendant 10 jours</t>
+          <t xml:space="preserve">1 injection sous-cutanée par cycle, 24 heures après la fin de la chimiothérapie (J2)</t>
         </is>
       </c>
       <c r="C100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antiseptique urinaire</t>
+          <t xml:space="preserve">Facteur de croissance (G-CSF à action prolongée)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NIVESTIM (filgrastim) 30 MU</t>
+          <t xml:space="preserve">NEUPOGEN (filgrastim) 48 MU</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 injection sous-cutanée par jour pendant 3 jours (de J2 à J4 après la chimiothérapie)</t>
+          <t xml:space="preserve">1 injection sous-cutanée par jour pendant 5 jours (de J2 à J6 après la chimiothérapie)</t>
         </is>
       </c>
       <c r="C101" t="inlineStr" s="2">
@@ -1805,1058 +1797,1109 @@
     <row r="102">
       <c r="A102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOCAND 50 mg</t>
+          <t xml:space="preserve">NIBIOL FORTE (nitroxoline) 100 mg</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé le matin pendant 7 jours</t>
+          <t xml:space="preserve">1 comprimé matin, midi et soir (soit 3 comprimés par jour) pendant 10 jours</t>
         </is>
       </c>
       <c r="C102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Antiseptique urinaire</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NORMACOL lavement</t>
+          <t xml:space="preserve">NIVESTIM (filgrastim) 30 MU</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 lavement en l'absence de selles pendant 3 jours malgré les autres traitements (MOVICOL…)</t>
+          <t xml:space="preserve">1 injection sous-cutanée par jour pendant 3 jours (de J2 à J4 après la chimiothérapie)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Laxatif (lavement rectal)</t>
+          <t xml:space="preserve">Facteur de croissance (G-CSF)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">OEDES (oméprazole) 20 mg</t>
+          <t xml:space="preserve">NOCAND 50 mg</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 gélule le matin</t>
+          <t xml:space="preserve">1 comprimé le matin pendant 7 jours</t>
         </is>
       </c>
       <c r="C104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antiulcéreux (inhibiteur de la pompe à protons)</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">OFLOCET (ofloxacine) 200 mg</t>
+          <t xml:space="preserve">NORMACOL lavement</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé (200 mg) par jour pendant 5 jours</t>
+          <t xml:space="preserve">1 lavement en l'absence de selles pendant 3 jours malgré les autres traitements (MOVICOL…)</t>
         </is>
       </c>
       <c r="C105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antibiotique (fluoroquinolone)</t>
+          <t xml:space="preserve">Laxatif (lavement rectal)</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">OLANZAPINE (ZYPREXA) 5 mg</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">1 comprimé le soir, de J1 à J4 de la chimiothérapie</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Antiémétique (neuroleptique)</t>
+      <c r="A106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">OEDES (oméprazole) 20 mg</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 gélule le matin</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Antiulcéreux (inhibiteur de la pompe à protons)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">OMIX (tamsulosine) 0,4 mg</t>
+          <t xml:space="preserve">OFLOCET (ofloxacine) 200 mg</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé le soir</t>
+          <t xml:space="preserve">1 comprimé (200 mg) par jour pendant 5 jours</t>
         </is>
       </c>
       <c r="C107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Alpha-bloquant (troubles urinaires)</t>
+          <t xml:space="preserve">Antibiotique (fluoroquinolone)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ORGOVYX (rélugolix) 120 mg</t>
+          <t xml:space="preserve">OLANZAPINE (ZYPREXA) 5 mg</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3 comprimés le 1er jour, puis 1 comprimé par jour</t>
+          <t xml:space="preserve">1 comprimé le soir, de J1 à J4 de la chimiothérapie</t>
         </is>
       </c>
       <c r="C108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Hormonothérapie anticancéreuse (antagoniste de la GnRH)</t>
+          <t xml:space="preserve">Antiémétique (neuroleptique)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">OROCAL VITAMINE D3 500 mg / 400 UI</t>
+          <t xml:space="preserve">OMIX (tamsulosine) 0,4 mg</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé matin et soir (soit 2 comprimés par jour)</t>
+          <t xml:space="preserve">1 comprimé le soir</t>
         </is>
       </c>
       <c r="C109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Calcium + vitamine D</t>
+          <t xml:space="preserve">Alpha-bloquant (troubles urinaires)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PARACÉTAMOL 1 g</t>
+          <t xml:space="preserve">ORGOVYX (rélugolix) 120 mg</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé en cas de douleur, maximum 4 comprimés par jour (au moins 4 heures entre 2 prises)</t>
+          <t xml:space="preserve">3 comprimés le 1er jour, puis 1 comprimé par jour</t>
         </is>
       </c>
       <c r="C110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antalgique et antipyrétique (palier 1)</t>
+          <t xml:space="preserve">Hormonothérapie anticancéreuse (antagoniste de la GnRH)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PARACÉTAMOL CODÉINÉ</t>
+          <t xml:space="preserve">OROCAL VITAMINE D3 500 mg / 400 UI</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé en cas de douleur, maximum 4 comprimés par jour</t>
+          <t xml:space="preserve">1 comprimé matin et soir (soit 2 comprimés par jour)</t>
         </is>
       </c>
       <c r="C111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antalgique de palier 2 (paracétamol + codéine)</t>
+          <t xml:space="preserve">Calcium + vitamine D</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PENTASA (mésalazine) 1 g / 100 ml, suspension rectale</t>
+          <t xml:space="preserve">PARACÉTAMOL 1 g</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 lavement par jour, allongé sur le côté, pendant 2 semaines, puis selon les symptômes</t>
+          <t xml:space="preserve">1 comprimé en cas de douleur, maximum 4 comprimés par jour (au moins 4 heures entre 2 prises)</t>
         </is>
       </c>
       <c r="C112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Anti-inflammatoire intestinal (rectite)</t>
+          <t xml:space="preserve">Antalgique et antipyrétique (palier 1)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PENTASA (mésalazine) 1 g, suppositoire</t>
+          <t xml:space="preserve">PARACÉTAMOL CODÉINÉ</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 suppositoire le soir pendant 7 jours</t>
+          <t xml:space="preserve">1 comprimé en cas de douleur, maximum 4 comprimés par jour</t>
         </is>
       </c>
       <c r="C113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Anti-inflammatoire intestinal (rectite)</t>
+          <t xml:space="preserve">Antalgique de palier 2 (paracétamol + codéine)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PRIMPERAN (métoclopramide) 10 mg</t>
+          <t xml:space="preserve">PEMORIAL (pembrolizumab) 100 mg</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé matin, midi et soir (soit 3 comprimés par jour) en cas de nausées</t>
+          <t xml:space="preserve">2 flacons de 100 mg tous les 21 jours</t>
         </is>
       </c>
       <c r="C114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antiémétique (antidopaminergique)</t>
+          <t xml:space="preserve">Immunothérapie</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">PROLIA (dénosumab) 60 mg</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">1 injection sous-cutanée tous les 6 mois, avec calcium et vitamine D</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Anti-résorptif osseux (ostéoporose sous hormonothérapie)</t>
+      <c r="A115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PENTASA (mésalazine) 1 g / 100 ml, suspension rectale</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 lavement par jour, allongé sur le côté, pendant 2 semaines, puis selon les symptômes</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Anti-inflammatoire intestinal (rectite)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PYOSTACINE (pristinamycine) 500 mg</t>
+          <t xml:space="preserve">PENTASA (mésalazine) 1 g, suppositoire</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2 comprimés matin et soir (soit 4 comprimés = 2 g par jour) pendant 8 à 14 jours</t>
+          <t xml:space="preserve">1 suppositoire le soir pendant 7 jours</t>
         </is>
       </c>
       <c r="C116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antibiotique (synergistine)</t>
+          <t xml:space="preserve">Anti-inflammatoire intestinal (rectite)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RECTOLAX microlavement</t>
+          <t xml:space="preserve">PRIMPERAN (métoclopramide) 10 mg</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 lavement avant chaque séance de radiothérapie (quantité : au moins 10 lavements)</t>
+          <t xml:space="preserve">1 comprimé matin, midi et soir (soit 3 comprimés par jour) en cas de nausées</t>
         </is>
       </c>
       <c r="C117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Laxatif (lavement rectal)</t>
+          <t xml:space="preserve">Antiémétique (antidopaminergique)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOPODERM (scopolamine) 1 mg / 72 h</t>
+          <t xml:space="preserve">PROLIA (dénosumab) 60 mg</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 patch derrière l'oreille, à changer toutes les 72 heures (garder 3 jours), pendant 1 mois</t>
+          <t xml:space="preserve">1 injection sous-cutanée tous les 6 mois, avec calcium et vitamine D</t>
         </is>
       </c>
       <c r="C118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Anticholinergique (antiémétique, anti-sécrétoire)</t>
+          <t xml:space="preserve">Anti-résorptif osseux (ostéoporose sous hormonothérapie)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SEDASTERIL crème lavante PM</t>
+          <t xml:space="preserve">PYOSTACINE (pristinamycine) 500 mg</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pour la toilette intime, chaque jour</t>
+          <t xml:space="preserve">2 comprimés matin et soir (soit 4 comprimés = 2 g par jour) pendant 8 à 14 jours</t>
         </is>
       </c>
       <c r="C119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Hygiène intime</t>
+          <t xml:space="preserve">Antibiotique (synergistine)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SEDASTERIL gel lubrifiant</t>
+          <t xml:space="preserve">RECTOLAX microlavement</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 à 2 applications par jour sur la zone vulvaire, ou avant les rapports sexuels</t>
+          <t xml:space="preserve">1 lavement avant chaque séance de radiothérapie (quantité : au moins 10 lavements)</t>
         </is>
       </c>
       <c r="C120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Lubrifiant intime</t>
+          <t xml:space="preserve">Laxatif (lavement rectal)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SEVREDOL (sulfate de morphine) 10 mg</t>
+          <t xml:space="preserve">SCOPODERM (scopolamine) 1 mg / 72 h</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé en cas de pic de douleur, maximum 6 comprimés par jour (au moins 1 heure entre 2 prises)</t>
+          <t xml:space="preserve">1 patch derrière l'oreille, à changer toutes les 72 heures (garder 3 jours), pendant 1 mois</t>
         </is>
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antalgique de palier 3 (morphine à libération immédiate)</t>
+          <t xml:space="preserve">Anticholinergique (antiémétique, anti-sécrétoire)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SMECTA (diosmectite) 3 g</t>
+          <t xml:space="preserve">SEDASTERIL crème lavante PM</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 à 2 sachets en cas de diarrhée légère, maximum 6 sachets par jour</t>
+          <t xml:space="preserve">Pour la toilette intime, chaque jour</t>
         </is>
       </c>
       <c r="C122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antidiarrhéique</t>
+          <t xml:space="preserve">Hygiène intime</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SPASFON LYOC (phloroglucinol)</t>
+          <t xml:space="preserve">SEDASTERIL gel lubrifiant</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 à 2 comprimés en cas de douleurs abdominales, maximum 6 comprimés par jour</t>
+          <t xml:space="preserve">1 à 2 applications par jour sur la zone vulvaire, ou avant les rapports sexuels</t>
         </is>
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antispasmodique</t>
+          <t xml:space="preserve">Lubrifiant intime</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">SULFARLEM S 25 (anétholtrithione)</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">1 comprimé matin, midi et soir (soit 3 comprimés par jour), avant les repas</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Sialagogue (sécheresse buccale)</t>
+      <c r="A124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SEVREDOL (sulfate de morphine) 10 mg</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 comprimé en cas de pic de douleur, maximum 6 comprimés par jour (au moins 1 heure entre 2 prises)</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Antalgique de palier 3 (morphine à libération immédiate)</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SYMBICORT TURBUHALER (budésonide + formotérol) 200 / 6 µg</t>
+          <t xml:space="preserve">SMECTA (diosmectite) 3 g</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 inhalation matin et soir (soit 2 inhalations par jour) pendant 1 mois</t>
+          <t xml:space="preserve">1 à 2 sachets en cas de diarrhée légère, maximum 6 sachets par jour</t>
         </is>
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antiasthmatique (corticoïde + bronchodilatateur)</t>
+          <t xml:space="preserve">Antidiarrhéique</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TADALAFIL 10 mg</t>
+          <t xml:space="preserve">SPASFON LYOC (phloroglucinol)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé au moins 30 minutes avant l'activité sexuelle (maximum 1 par jour), pendant 3 mois</t>
+          <t xml:space="preserve">1 à 2 comprimés en cas de douleurs abdominales, maximum 6 comprimés par jour</t>
         </is>
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Traitement de la dysfonction érectile (inhibiteur de la PDE5)</t>
+          <t xml:space="preserve">Antispasmodique</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TADALAFIL 20 mg</t>
+          <t xml:space="preserve">SULFARLEM S 25 (anétholtrithione)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé au moins 30 minutes avant l'activité sexuelle (maximum 1 par jour), pendant 3 mois</t>
+          <t xml:space="preserve">1 comprimé matin, midi et soir (soit 3 comprimés par jour), avant les repas</t>
         </is>
       </c>
       <c r="C127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Traitement de la dysfonction érectile (inhibiteur de la PDE5)</t>
+          <t xml:space="preserve">Sialagogue (sécheresse buccale)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TADALAFIL 5 mg</t>
+          <t xml:space="preserve">SYMBICORT TURBUHALER (budésonide + formotérol) 200 / 6 µg</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé par jour, le matin, pendant 3 mois</t>
+          <t xml:space="preserve">1 inhalation matin et soir (soit 2 inhalations par jour) pendant 1 mois</t>
         </is>
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">Antiasthmatique (corticoïde + bronchodilatateur)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TADALAFIL 10 mg</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 comprimé au moins 30 minutes avant l'activité sexuelle (maximum 1 par jour), pendant 3 mois</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">Traitement de la dysfonction érectile (inhibiteur de la PDE5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">TAGRISSO (osimertinib) 80 mg</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">1 comprimé par jour, à heure fixe, pendant ou en dehors des repas</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Thérapie ciblée (inhibiteur de l'EGFR)</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TAMOXIFÈNE 20 mg</t>
+          <t xml:space="preserve">TADALAFIL 20 mg</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé par jour, à heure fixe, pendant 3 mois</t>
+          <t xml:space="preserve">1 comprimé au moins 30 minutes avant l'activité sexuelle (maximum 1 par jour), pendant 3 mois</t>
         </is>
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Hormonothérapie anticancéreuse (anti-œstrogène)</t>
+          <t xml:space="preserve">Traitement de la dysfonction érectile (inhibiteur de la PDE5)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TANGANIL B20, comprimé</t>
+          <t xml:space="preserve">TADALAFIL 5 mg</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé matin, midi et soir (soit 3 comprimés par jour) pendant 1 mois</t>
+          <t xml:space="preserve">1 comprimé par jour, le matin, pendant 3 mois</t>
         </is>
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antivertigineux (acétylleucine)</t>
+          <t xml:space="preserve">Traitement de la dysfonction érectile (inhibiteur de la PDE5)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TAVANIC (lévofloxacine) 500 mg</t>
+          <t xml:space="preserve">TAGRISSO (osimertinib) 80 mg</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé (500 mg) le 1er jour, puis ½ comprimé (250 mg) par jour pendant 5 jours</t>
+          <t xml:space="preserve">1 comprimé par jour, à heure fixe, pendant ou en dehors des repas</t>
         </is>
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antibiotique (fluoroquinolone)</t>
+          <t xml:space="preserve">Thérapie ciblée (inhibiteur de l'EGFR)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TEGUMA (terbinafine) 250 mg</t>
+          <t xml:space="preserve">TAMOXIFÈNE 20 mg</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé matin et soir soit 2 comprimés par jour</t>
+          <t xml:space="preserve">1 comprimé par jour, à heure fixe, pendant 3 mois</t>
         </is>
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antifongique</t>
+          <t xml:space="preserve">Hormonothérapie anticancéreuse (anti-œstrogène)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TEMODAL (témozolomide) 75 mg/m²/jour</t>
+          <t xml:space="preserve">TANGANIL B20, comprimé</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 prise par jour, à jeun, 1 h 30 avant la radiothérapie, tous les jours du début à la fin de la radiothérapie</t>
+          <t xml:space="preserve">1 comprimé matin, midi et soir (soit 3 comprimés par jour) pendant 1 mois</t>
         </is>
       </c>
       <c r="C134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Chimiothérapie orale (agent alkylant)</t>
+          <t xml:space="preserve">Antivertigineux (acétylleucine)</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">TEMODAL (témozolomide), phase adjuvante</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">1 prise par jour, à jeun, 5 jours de suite (J1 à J5) tous les 28 jours : 150 mg/m² par jour au 1er cycle, puis 200 mg/m² par jour si bonne tolérance (gélules de … mg)</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Chimiothérapie orale (agent alkylant)</t>
+      <c r="A135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TAVANIC (lévofloxacine) 500 mg</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 comprimé (500 mg) le 1er jour, puis ½ comprimé (250 mg) par jour pendant 5 jours</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Antibiotique (fluoroquinolone)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TIORFAN (racécadotril) 100 mg</t>
+          <t xml:space="preserve">TEGUMA (terbinafine) 250 mg</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 à 2 gélules si les diarrhées importantes persistent sous LOPERIUM, maximum 6 gélules par jour</t>
+          <t xml:space="preserve">1 comprimé le matin pendant 7 jours</t>
         </is>
       </c>
       <c r="C136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antidiarrhéique (anti-sécrétoire)</t>
+          <t xml:space="preserve">Antifongique</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TITANORÉINE à la lidocaïne 2 % crème</t>
+          <t xml:space="preserve">TEMODAL (témozolomide) 75 mg/m²/jour</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 application avant et après chaque selle, maximum 4 applications par jour</t>
+          <t xml:space="preserve">1 prise par jour, à jeun, 1 h 30 avant la radiothérapie, tous les jours du début à la fin de la radiothérapie</t>
         </is>
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antihémorroïdaire</t>
+          <t xml:space="preserve">Chimiothérapie orale (agent alkylant)</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TITANORÉINE suppositoire</t>
+          <t xml:space="preserve">TEMODAL (témozolomide), phase adjuvante</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 à 2 suppositoires par jour jusqu'à cicatrisation</t>
+          <t xml:space="preserve">1 prise par jour, à jeun, 5 jours de suite (J1 à J5) tous les 28 jours : 150 mg/m² par jour au 1er cycle, puis 200 mg/m² par jour si bonne tolérance (gélules de … mg)</t>
         </is>
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antihémorroïdaire</t>
+          <t xml:space="preserve">Chimiothérapie orale (agent alkylant)</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TOLÉRIANE crème légère</t>
+          <t xml:space="preserve">TIORFAN (racécadotril) 100 mg</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 application par jour, le matin</t>
+          <t xml:space="preserve">1 à 2 gélules si les diarrhées importantes persistent sous LOPERIUM, maximum 6 gélules par jour</t>
         </is>
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Soin dermatologique apaisant</t>
+          <t xml:space="preserve">Antidiarrhéique (anti-sécrétoire)</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TRAMAL (tramadol) 50 mg</t>
+          <t xml:space="preserve">TITANORÉINE à la lidocaïne 2 % crème</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé en cas de douleur, maximum 6 comprimés par jour (au moins 4 heures entre 2 prises)</t>
+          <t xml:space="preserve">1 application avant et après chaque selle, maximum 4 applications par jour</t>
         </is>
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antalgique de palier 2 (tramadol)</t>
+          <t xml:space="preserve">Antihémorroïdaire</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TRAMAL LP (tramadol) 100 mg</t>
+          <t xml:space="preserve">TITANORÉINE suppositoire</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé le matin et 1 comprimé le soir (toutes les 12 heures)</t>
+          <t xml:space="preserve">1 à 2 suppositoires par jour jusqu'à cicatrisation</t>
         </is>
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antalgique de palier 2 (tramadol à libération prolongée)</t>
+          <t xml:space="preserve">Antihémorroïdaire</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UROREC (silodosine) 4 mg</t>
+          <t xml:space="preserve">TOLÉRIANE crème légère</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 gélule le soir pendant 3 mois</t>
+          <t xml:space="preserve">1 application par jour, le matin</t>
         </is>
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Alpha-bloquant (troubles urinaires)</t>
+          <t xml:space="preserve">Soin dermatologique apaisant</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UROREC (silodosine) 8 mg</t>
+          <t xml:space="preserve">TRAMAL (tramadol) 50 mg</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 gélule le soir pendant 3 mois</t>
+          <t xml:space="preserve">1 comprimé en cas de douleur, maximum 6 comprimés par jour (au moins 4 heures entre 2 prises)</t>
         </is>
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Alpha-bloquant (troubles urinaires)</t>
+          <t xml:space="preserve">Antalgique de palier 2 (tramadol)</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UVEDOSE 100 000 UI, solution buvable</t>
+          <t xml:space="preserve">TRAMAL LP (tramadol) 100 mg</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 ampoule par mois à boire sur un sucre pendant 2 mois, puis 1 ampoule tous les 3 mois</t>
+          <t xml:space="preserve">1 comprimé le matin et 1 comprimé le soir (toutes les 12 heures)</t>
         </is>
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Vitamine D</t>
+          <t xml:space="preserve">Antalgique de palier 2 (tramadol à libération prolongée)</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VASELINE stérile</t>
+          <t xml:space="preserve">UROREC (silodosine) 4 mg</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 à 2 applications par jour, en couche épaisse, sur les lésions suintantes et croûteuses</t>
+          <t xml:space="preserve">1 gélule le soir pendant 3 mois</t>
         </is>
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Émollient</t>
+          <t xml:space="preserve">Alpha-bloquant (troubles urinaires)</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VECA (solifénacine) 10 mg</t>
+          <t xml:space="preserve">UROREC (silodosine) 8 mg</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé le soir pendant 1 mois en cas de brûlures mictionnelles</t>
+          <t xml:space="preserve">1 gélule le soir pendant 3 mois</t>
         </is>
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antispasmodique urinaire (anticholinergique)</t>
+          <t xml:space="preserve">Alpha-bloquant (troubles urinaires)</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VECA (solifénacine) 5 mg</t>
+          <t xml:space="preserve">UVEDOSE 100 000 UI, solution buvable</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé le soir pendant 1 mois en cas de brûlures mictionnelles</t>
+          <t xml:space="preserve">1 ampoule par mois à boire sur un sucre pendant 2 mois, puis 1 ampoule tous les 3 mois</t>
         </is>
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antispasmodique urinaire (anticholinergique)</t>
+          <t xml:space="preserve">Vitamine D</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VENTOLINE (salbutamol) 2,5 mg / 2,5 ml, solution pour nébuliseur</t>
+          <t xml:space="preserve">VASELINE stérile</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 nébulisation en cas de difficulté respiratoire, maximum 4 par jour</t>
+          <t xml:space="preserve">1 à 2 applications par jour, en couche épaisse, sur les lésions suintantes et croûteuses</t>
         </is>
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Bronchodilatateur (bêta-2 agoniste)</t>
+          <t xml:space="preserve">Émollient</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">VERZENIOS (abémaciclib) 150 mg</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">1 comprimé matin et soir (soit 300 mg par jour), en continu, avec l'hormonothérapie</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Thérapie ciblée (inhibiteur de CDK4/6)</t>
+      <c r="A149" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">VECA (solifénacine) 10 mg</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 comprimé le soir pendant 1 mois en cas de brûlures mictionnelles</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Antispasmodique urinaire (anticholinergique)</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VITANEVRIL FORTE</t>
+          <t xml:space="preserve">VECA (solifénacine) 5 mg</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé matin et soir (soit 2 comprimés par jour) pendant 3 mois</t>
+          <t xml:space="preserve">1 comprimé le soir pendant 1 mois en cas de brûlures mictionnelles</t>
         </is>
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Vitamines B (neurotropes)</t>
+          <t xml:space="preserve">Antispasmodique urinaire (anticholinergique)</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">XATRAL LP (alfuzosine) 10 mg</t>
+          <t xml:space="preserve">VENTOLINE (salbutamol) 2,5 mg / 2,5 ml, solution pour nébuliseur</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé par jour, après le repas du soir</t>
+          <t xml:space="preserve">1 nébulisation en cas de difficulté respiratoire, maximum 4 par jour</t>
         </is>
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Alpha-bloquant (troubles urinaires)</t>
+          <t xml:space="preserve">Bronchodilatateur (bêta-2 agoniste)</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">XGEVA (dénosumab) 120 mg</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">1 injection sous-cutanée toutes les 4 semaines, avec calcium et vitamine D</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Anti-résorptif osseux (métastases osseuses)</t>
+      <c r="A152" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">VERZENIOS (abémaciclib) 150 mg</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 comprimé matin et soir (soit 300 mg par jour), en continu, avec l'hormonothérapie</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Thérapie ciblée (inhibiteur de CDK4/6)</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">XTANDI (enzalutamide) 40 mg</t>
+          <t xml:space="preserve">VITANEVRIL FORTE</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4 comprimés par jour en une seule prise le matin (soit 160 mg par jour)</t>
+          <t xml:space="preserve">1 comprimé matin et soir (soit 2 comprimés par jour) pendant 3 mois</t>
         </is>
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Hormonothérapie anticancéreuse (anti-androgène)</t>
+          <t xml:space="preserve">Vitamines B (neurotropes)</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">XYLITOL chewing-gum</t>
+          <t xml:space="preserve">XATRAL LP (alfuzosine) 10 mg</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">À mâcher selon les besoins, jusqu'à 4 fois par jour</t>
+          <t xml:space="preserve">1 comprimé par jour, après le repas du soir</t>
         </is>
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sécheresse buccale (stimulation salivaire)</t>
+          <t xml:space="preserve">Alpha-bloquant (troubles urinaires)</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">XYLOCAÏNE VISQUEUSE (lidocaïne) 2 % gel</t>
+          <t xml:space="preserve">XGEVA (dénosumab) 120 mg</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 application sur les zones douloureuses, après les repas ou au moins 1 heure avant</t>
+          <t xml:space="preserve">1 injection sous-cutanée toutes les 4 semaines, avec calcium et vitamine D</t>
         </is>
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Anesthésique local</t>
+          <t xml:space="preserve">Anti-résorptif osseux (métastases osseuses)</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">YOFOLVIT (acide folique)</t>
+          <t xml:space="preserve">XTANDI (enzalutamide) 40 mg</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé par jour, le matin, pendant 3 mois</t>
+          <t xml:space="preserve">4 comprimés par jour en une seule prise le matin (soit 160 mg par jour)</t>
         </is>
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Vitamine B9 (acide folique)</t>
+          <t xml:space="preserve">Hormonothérapie anticancéreuse (anti-androgène)</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ZETALAX, microlavement</t>
+          <t xml:space="preserve">XYLITOL chewing-gum</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 lavement avant chaque séance de radiothérapie (quantité : au moins 10 lavements)</t>
+          <t xml:space="preserve">À mâcher selon les besoins, jusqu'à 4 fois par jour</t>
         </is>
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Laxatif (lavement rectal)</t>
+          <t xml:space="preserve">Sécheresse buccale (stimulation salivaire)</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ZOLADEX (goséréline) 3,6 mg</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">1 injection sous-cutanée tous les 28 jours</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Hormonothérapie anticancéreuse (agoniste de la LH-RH)</t>
+      <c r="A158" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">XYLOCAÏNE VISQUEUSE (lidocaïne) 2 % gel</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 application sur les zones douloureuses, après les repas ou au moins 1 heure avant</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Anesthésique local</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ZOLADEX LP (goséréline) 10,8 mg</t>
+          <t xml:space="preserve">YOFOLVIT (acide folique)</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 injection sous-cutanée tous les 3 mois</t>
+          <t xml:space="preserve">1 comprimé par jour, le matin, pendant 3 mois</t>
         </is>
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Hormonothérapie anticancéreuse (agoniste de la LH-RH)</t>
+          <t xml:space="preserve">Vitamine B9 (acide folique)</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ZOMETA (acide zolédronique) 4 mg</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">1 perfusion intraveineuse de 15 minutes toutes les 4 semaines (ou toutes les 12 semaines)</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">Bisphosphonate (métastases osseuses)</t>
+      <c r="A160" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ZETALAX, microlavement</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 lavement avant chaque séance de radiothérapie (quantité : au moins 10 lavements)</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Laxatif (lavement rectal)</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ZOPHREN (ondansétron) 8 mg</t>
+          <t xml:space="preserve">ZOLADEX (goséréline) 3,6 mg</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé matin et soir (soit 2 comprimés par jour) à J1, J2 et J3 après la chimiothérapie (pendant 3 jours)</t>
+          <t xml:space="preserve">1 injection sous-cutanée tous les 28 jours</t>
         </is>
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antiémétique (sétron, anti-5HT3)</t>
+          <t xml:space="preserve">Hormonothérapie anticancéreuse (agoniste de la LH-RH)</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ZOPHREN (ondansétron) 8 mg</t>
+          <t xml:space="preserve">ZOLADEX LP (goséréline) 10,8 mg</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 comprimé si les nausées persistent, maximum 2 comprimés par jour (espacés de 12 heures)</t>
+          <t xml:space="preserve">1 injection sous-cutanée tous les 3 mois</t>
         </is>
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Antiémétique (sétron, anti-5HT3)</t>
+          <t xml:space="preserve">Hormonothérapie anticancéreuse (agoniste de la LH-RH)</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">ZOMETA (acide zolédronique) 4 mg</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 perfusion intraveineuse de 15 minutes toutes les 4 semaines (ou toutes les 12 semaines)</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Bisphosphonate (métastases osseuses)</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ZOPHREN (ondansétron) 8 mg</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 comprimé matin et soir (soit 2 comprimés par jour) à J1, J2 et J3 après la chimiothérapie (pendant 3 jours)</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Antiémétique (sétron, anti-5HT3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ZOPHREN (ondansétron) 8 mg</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1 comprimé si les nausées persistent, maximum 2 comprimés par jour (espacés de 12 heures)</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Antiémétique (sétron, anti-5HT3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">ZYTIGA (abiratérone) 250 mg</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr" s="2">
+      <c r="B166" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">4 comprimés le matin en une seule prise, à jeun (au moins 2 heures après un repas et 1 heure avant le suivant), avec un grand verre d'eau (soit 1 000 mg par jour)</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr" s="2">
+      <c r="C166" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Hormonothérapie anticancéreuse (inhibiteur de la synthèse des androgènes)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C163"/>
+  <autoFilter ref="A1:C166"/>
 </worksheet>
 </file>